--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ANSI 62</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ANSI 63</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANSI 64</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ANSI 65</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ANSI 66</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ANSI 67</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ANSI 68</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ANSI 69</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ANSI 70</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>125al</t>
+          <t>125AL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANSI 71</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ANSI 72</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ANSI 73</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ANSI 74</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ANSI 75</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -767,87 +767,6 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PP19380-03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PP19380-03-12gacr-ANSI 73</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>11.035x43.7</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PP19568-02</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PP19568-02-16gacr-ANSI 74</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>16.22x36.09</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PP22114-05</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PP22114-05-12gacr-ANSI 75</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>16.035x35.7</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>16gacr</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>16gacr</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 62</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>12gacr</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 63</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>16gacr</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 64</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>14gacr</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 65</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>14gacr</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 66</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>12gacr</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 67</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>12gacr</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 68</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>12gacr</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 69</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>14gacr</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 70</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>125AL</t>
+          <t>125al</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 71</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>16gacr</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -763,7 +763,88 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 72</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PP19380-03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PP19380-03-12gacr-ANSI 73</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>11.035x43.7</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ANSI 73</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PP19568-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PP19568-02-16gacr-ANSI 74</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>16.22x36.09</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ANSI 74</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PP22114-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PP22114-05-12gacr-ANSI 75</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16.035x35.7</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ANSI 75</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ANSI 62</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ANSI 63</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANSI 64</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ANSI 65</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ANSI 66</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ANSI 67</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ANSI 68</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ANSI 69</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ANSI 70</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P19657-26-16gacr-ANSI 62</t>
+          <t>P19657-26-16gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P19660-14-12gacr-ANSI 63</t>
+          <t>P19660-14-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P19671-05-16gacr-ANSI 64</t>
+          <t>P19671-05-16gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P20321S-08-01-14gacr-ANSI 65</t>
+          <t>P20321S-08-01-14gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P20321S-08-02-14gacr-ANSI 66</t>
+          <t>P20321S-08-02-14gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P20325-23-12gacr-ANSI 67</t>
+          <t>P20325-23-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P20330-02-12gacr-ANSI 68</t>
+          <t>P20330-02-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P20336-01-12gacr-ANSI 69</t>
+          <t>P20336-01-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PP10315-01-14gacr-ANSI 70</t>
+          <t>PP10315-01-14gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PP1094-125al-ANSI 71</t>
+          <t>PP1094-125al-ANSI 61</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PP13629-12-16gacr-ANSI 72</t>
+          <t>PP13629-12-16gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PP19380-03-12gacr-ANSI 73</t>
+          <t>PP19380-03-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PP19568-02-16gacr-ANSI 74</t>
+          <t>PP19568-02-16gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PP22114-05-12gacr-ANSI 75</t>
+          <t>PP22114-05-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>125al</t>
+          <t>125AL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANSI 71</t>
+          <t>Otro</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ANSI 72</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ANSI 73</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ANSI 74</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ANSI 75</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P19657-25</t>
+          <t>11-B-9016-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P19657-25-16gacr-ANSI 61</t>
+          <t>11-B-9016-01SD Iuiu fdshfkjhal jkhfdslkj</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -461,388 +461,10 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.093x48.72</t>
+          <t>Angulo 1.25 x 2.25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>P19657-26</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P19657-26-16gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>18.093x48.72</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>P19660-14</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P19660-14-12gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>21.08x43.7</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>P19671-05</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P19671-05-16gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>44.09x18.72</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P20321S-08-01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P20321S-08-01-14gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>14GACR</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>21.18x35.18</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>P20321S-08-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P20321S-08-02-14gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>14GACR</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>21.18x35.18</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P20325-23</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P20325-23-12gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>16.035x43.7</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>P20330-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P20330-02-12gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>29.702x76.082</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>P20336-01</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>P20336-01-12gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>21.035x35.7</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PP10315-01</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PP10315-01-14gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>14GACR</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>44.032x31.162</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PP1094</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PP1094-125al-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>125AL</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5.668x90</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PP13629-12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PP13629-12-16gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>17.485x11.03</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PP19380-03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PP19380-03-12gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>11.035x43.7</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PP19568-02</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PP19568-02-16gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>16.22x36.09</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PP22114-05</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PP22114-05-12gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>16.035x35.7</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
         <is>
           <t>Ansi 61</t>
         </is>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>Acabado_Superficial</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Es_Nuevo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -451,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11-B-9016-01SD Iuiu fdshfkjhal jkhfdslkj</t>
+          <t>ING0001 - 11-B-9016-01-(12gacr ANSI-61) - K30 - V0-R0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,6 +473,9 @@
         <is>
           <t>Ansi 61</t>
         </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,456 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P19657-25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P19657-25-16gacr-ANSI 61</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>16.093x48.72</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P19657-26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P19657-26-16gacr-ANSI 62</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>18.093x48.72</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ANSI 62</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P19660-14</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P19660-14-12gacr-ANSI 63</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>21.08x43.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ANSI 63</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P19671-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>P19671-05-16gacr-ANSI 64</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>44.09x18.72</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ANSI 64</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P20321S-08-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P20321S-08-01-14gacr-ANSI 65</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14gacr</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>21.18x35.18</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ANSI 65</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P20321S-08-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P20321S-08-02-14gacr-ANSI 66</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14gacr</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>21.18x35.18</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ANSI 66</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P20325-23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P20325-23-12gacr-ANSI 67</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>16.035x43.7</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ANSI 67</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P20330-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P20330-02-12gacr-ANSI 68</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>29.702x76.082</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ANSI 68</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P20336-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P20336-01-12gacr-ANSI 69</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>21.035x35.7</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ANSI 69</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PP10315-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PP10315-01-14gacr-ANSI 70</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14gacr</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>44.032x31.162</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ANSI 70</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PP1094</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PP1094-125al-ANSI 71</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>125al</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5.668x90</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ANSI 71</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PP13629-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PP13629-12-16gacr-ANSI 72</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>17.485x11.03</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ANSI 72</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PP19380-03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PP19380-03-12gacr-ANSI 73</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>11.035x43.7</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ANSI 73</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PP19568-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PP19568-02-16gacr-ANSI 74</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16.22x36.09</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ANSI 74</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PP22114-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PP22114-05-12gacr-ANSI 75</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>16.035x35.7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ANSI 75</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P19657-26-16gacr-ANSI 62</t>
+          <t>P19657-26-16gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ANSI 62</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -546,7 +546,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P19660-14-12gacr-ANSI 63</t>
+          <t>P19660-14-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANSI 63</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -576,7 +576,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P19671-05-16gacr-ANSI 64</t>
+          <t>P19671-05-16gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ANSI 64</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -606,7 +606,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P20321S-08-01-14gacr-ANSI 65</t>
+          <t>P20321S-08-01-14gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ANSI 65</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -636,7 +636,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P20321S-08-02-14gacr-ANSI 66</t>
+          <t>P20321S-08-02-14gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ANSI 66</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -666,7 +666,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P20325-23-12gacr-ANSI 67</t>
+          <t>P20325-23-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ANSI 67</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P20330-02-12gacr-ANSI 68</t>
+          <t>P20330-02-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ANSI 68</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -726,7 +726,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P20336-01-12gacr-ANSI 69</t>
+          <t>P20336-01-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ANSI 69</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -756,7 +756,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PP10315-01-14gacr-ANSI 70</t>
+          <t>PP10315-01-14gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANSI 70</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -786,7 +786,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PP1094-125al-ANSI 71</t>
+          <t>PP1094-125al-ANSI 61</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ANSI 71</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -816,7 +816,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PP13629-12-16gacr-ANSI 72</t>
+          <t>PP13629-12-16gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ANSI 72</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -846,7 +846,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PP19380-03-12gacr-ANSI 73</t>
+          <t>PP19380-03-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ANSI 73</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -876,7 +876,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PP19568-02-16gacr-ANSI 74</t>
+          <t>PP19568-02-16gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ANSI 74</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -906,7 +906,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PP22114-05-12gacr-ANSI 75</t>
+          <t>PP22114-05-12gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ANSI 75</t>
+          <t>ANSI 61</t>
         </is>
       </c>
       <c r="F17" t="b">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -521,7 +521,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -551,7 +551,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -581,7 +581,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -611,7 +611,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -641,7 +641,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -671,7 +671,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -701,7 +701,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -731,7 +731,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -761,7 +761,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -791,7 +791,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>125al</t>
+          <t>125AL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -821,7 +821,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -851,7 +851,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -881,7 +881,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -911,7 +911,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F17" t="b">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11-B-9016-01</t>
+          <t>P19657-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11-B-9016-01SD Iuiu fdshfkjhal jkhfdslkj</t>
+          <t>P19657-25-16gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -461,10 +461,307 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Angulo 1.25 x 2.25</t>
+          <t>16.093x48.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P19657-26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P19657-26-16gacr-ANSI 62</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>18.093x48.72</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P19660-14</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P19660-14-12gacr-ANSI 63</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>21.08x43.7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P19671-05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P19671-05-16gacr-ANSI 64</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>44.09x18.72</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P20321S-08-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>P20321S-08-01-14gacr-ANSI 65</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>21.18x35.18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P20321S-08-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P20321S-08-02-14gacr-ANSI 66</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>21.18x35.18</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P20325-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P20325-23-12gacr-ANSI 67</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>16.035x43.7</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P20330-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P20330-02-12gacr-ANSI 68</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>29.702x76.082</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P20336-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P20336-01-12gacr-ANSI 69</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>21.035x35.7</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PP10315-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PP10315-01-14gacr-ANSI 70</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>44.032x31.162</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PP1094</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PP1094-125al-ANSI 71</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>125AL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.668x90</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PP13629-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PP13629-12-16gacr-ANSI 72</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>17.485x11.03</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Ansi 61</t>
         </is>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,114 +659,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>P20336-01</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>P20336-01-12gacr-ANSI 69</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>21.035x35.7</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PP10315-01</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PP10315-01-14gacr-ANSI 70</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>14GACR</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>44.032x31.162</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PP1094</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PP1094-125al-ANSI 71</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>125AL</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5.668x90</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PP13629-12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PP13629-12-16gacr-ANSI 72</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>17.485x11.03</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,6 +659,33 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>11-B-9016-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11-B-9016-01SD Iuiu fdshfkjhal jkhfdslkj</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Angulo 1.25 x 2.25</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11-B-9016-01SD Iuiu fdshfkjhal jkhfdslkj</t>
+          <t>11-B-9016-01-(12gacr ANSI-61) - K30 - V0-R0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -446,22 +446,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P19657-25</t>
+          <t>11-B-9016-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P19657-25-16gacr-ANSI 61</t>
+          <t>11-B-9016-01-(12gacr ANSI-61) - K30 - V0-R0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.093x48.72</t>
+          <t>Angulo 1.25 x 2.25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -473,12 +473,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P19657-26</t>
+          <t>P19657-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P19657-26-16gacr-ANSI 62</t>
+          <t>P19657-25-16gacr-ANSI 61</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.093x48.72</t>
+          <t>16.093x48.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -500,22 +500,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P19660-14</t>
+          <t>P19657-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P19660-14-12gacr-ANSI 63</t>
+          <t>P19657-26-16gacr-ANSI 62</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.08x43.7</t>
+          <t>18.093x48.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -527,22 +527,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P19671-05</t>
+          <t>P19660-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P19671-05-16gacr-ANSI 64</t>
+          <t>P19660-14-12gacr-ANSI 63</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.09x18.72</t>
+          <t>21.08x43.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -554,22 +554,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P20321S-08-01</t>
+          <t>P19671-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P20321S-08-01-14gacr-ANSI 65</t>
+          <t>P19671-05-16gacr-ANSI 64</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>21.18x35.18</t>
+          <t>44.09x18.72</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -581,12 +581,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P20321S-08-02</t>
+          <t>P20321S-08-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P20321S-08-02-14gacr-ANSI 66</t>
+          <t>P20321S-08-01-14gacr-ANSI 65</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,22 +608,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P20325-23</t>
+          <t>P20321S-08-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P20325-23-12gacr-ANSI 67</t>
+          <t>P20321S-08-02-14gacr-ANSI 66</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16.035x43.7</t>
+          <t>21.18x35.18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P20330-02</t>
+          <t>P20325-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P20330-02-12gacr-ANSI 68</t>
+          <t>P20325-23-12gacr-ANSI 67</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>29.702x76.082</t>
+          <t>16.035x43.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -662,12 +662,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11-B-9016-01</t>
+          <t>P20330-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11-B-9016-01-(12gacr ANSI-61) - K30 - V0-R0</t>
+          <t>P20330-02-12gacr-ANSI 68</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Angulo 1.25 x 2.25</t>
+          <t>29.702x76.082</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,222 +465,6 @@
         </is>
       </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>P19657-25</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P19657-25-16gacr-ANSI 61</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>16.093x48.72</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>P19657-26</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P19657-26-16gacr-ANSI 62</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>18.093x48.72</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>P19660-14</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P19660-14-12gacr-ANSI 63</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>21.08x43.7</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P19671-05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P19671-05-16gacr-ANSI 64</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>44.09x18.72</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>P20321S-08-01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P20321S-08-01-14gacr-ANSI 65</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>14GACR</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>21.18x35.18</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P20321S-08-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P20321S-08-02-14gacr-ANSI 66</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>14GACR</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>21.18x35.18</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>P20325-23</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P20325-23-12gacr-ANSI 67</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>16.035x43.7</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>P20330-02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>P20330-02-12gacr-ANSI 68</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>12GACR</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>29.702x76.082</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>Ansi 61</t>
         </is>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,492 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P13704-101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P13704-101-(14gacr ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Length: 28.81 * Width: 21.19</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P13704-091</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P13704-091-(14gacr ANSI-61) - K48 - V5-R0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Length: 28.81 * Width: 24.88</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P13704-091</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P13704-091-(14gacr ANSI-61) - K48 - V5-R0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Length: 28.81 * Width: 24.88</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P13704-091</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>P13704-091-(14gacr ANSI-61) - K48 - V5-R0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Length: 28.81 * Width: 24.88</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PP21340-03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Length: 16.970 * Width: 15.000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12-D-6106-08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Length: 42.810 * Width: 9.940</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>12-D-6091-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Length: 29.94 * Width: 28.81</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12-D-6085-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Length: 34.81 * Width:  12.44</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>12-D-6091-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Length: 29.94 * Width: 28.81</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P19504-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Length: 28.81 * Width: 4.940</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12-D-6091-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Length: 29.94 * Width: 28.81</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12-D-6348-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Length: 34.810 * Width: 29.940</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12-D-6106-07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Length: 34.82 * Width: 9.94</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12-D-6091-04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Length: 29.940 * Width: 21.810</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Length: 29.940 * Width: 28.810</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Length: 29.940 * Width: 28.810</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Length: 29.940 * Width: 28.810</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFINIR NOMBRE </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Length: 29.940 * Width: 28.810</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,12 +581,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PP21340-03</t>
+          <t>11-A-6014-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>11-A-6014-01-(16ga ANSI-61) - K48 - V5-R0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -596,24 +596,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Length: 16.970 * Width: 15.000</t>
+          <t>Length: 34.81 * Width: 12.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12-D-6106-08</t>
+          <t>11-a-6004-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>11-A-6004-01-(16ga ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -623,24 +623,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Length: 42.810 * Width: 9.940</t>
+          <t>Length: 19.00 * Width: 3.50</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12-D-6091-06</t>
+          <t>12-6010-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -650,24 +650,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Length: 29.94 * Width: 28.81</t>
+          <t>Length: 19.00 * Width: 2.26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12-D-6085-06</t>
+          <t>12-6010-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -677,78 +677,78 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Length: 34.81 * Width:  12.44</t>
+          <t>Length: 19.00 * Width: 6.01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12-D-6091-06</t>
+          <t>12-A-6200-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>12-A-6200-02-(12gacr ANSI-61) - K47 - V4-R2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Length: 29.94 * Width: 28.81</t>
+          <t>Length: 29.70 * Width: 16.09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P19504-09</t>
+          <t>12-A-6359-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>12-A-6359-02-(12gacr ANSI-61) - K47 - V6-R3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Length: 28.81 * Width: 4.940</t>
+          <t>Length: 21.08 * Width: 35.70</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12-D-6091-06</t>
+          <t>12-C-6017-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>12-C-6017-01-(16ga ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -758,24 +758,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Length: 29.94 * Width: 28.81</t>
+          <t>Length: 28.81 * Width: 7.44</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12-D-6348-12</t>
+          <t>12-D-6047-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>12-D-6047-03-(16ga ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -785,24 +785,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Length: 34.810 * Width: 29.940</t>
+          <t>Length: 8.71 * Width: 44.08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12-D-6106-07</t>
+          <t>12-D-6063-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>12-D-6063-06-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -812,24 +812,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Length: 34.82 * Width: 9.94</t>
+          <t>Length: 9.97 * Width: 36.09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12-D-6091-04</t>
+          <t>12-D-6078-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>12-D-6078-05-(16ga ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -839,24 +839,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Length: 29.940 * Width: 21.810</t>
+          <t>Length: 3.71 * Width: 30.08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P6298-051</t>
+          <t>12-D-6080-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>12-D-6080-06-(16ga ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -866,24 +866,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Length: 29.940 * Width: 28.810</t>
+          <t>Length: 6.22 * Width: 36.09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P6298-051</t>
+          <t>12-D-6081-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>12-D-6081-06-(16ga ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -893,24 +893,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Length: 29.940 * Width: 28.810</t>
+          <t>Length: 7.47 * Width: 36.09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P6298-051</t>
+          <t>12-D-6082-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
+          <t>12-D-6082-05-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -920,39 +920,1011 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Length: 29.940 * Width: 28.810</t>
+          <t>Length: 8.71 * Width: 30.08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>12-D-6082-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12-D-6082-06-(16ga ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Length: 8.71 * Width: 36.08</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12-D-6083-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12-D-6083-06-(16ga ANSI-61) - K48 - V3-R0</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Length: 36.08 * Width: 11.21</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12-D-6088-08</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DEFINER NOMBRE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Length: 36.08 * Width: 21.21</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12-D-6091-03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12-D-6091-03-(16ga ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Length: 31.22 * Width: 18.09</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12-D-6091-08</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12-D-6091-08-(16ga ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Length: 31.22 * Width: 36.09</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12-c-6210-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DEFINER NOMBRE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Length: 8.71 * Width: 36.08</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>17-D-6004-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>17-D-6004-01-(16ga ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Length: 13.71 * Width: 23.09</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>17-D-6004-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>17-D-6004-02-(16ga ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Length: 31.16 * Width: 23.09</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>17-D-6007-01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17-D-6007-01-(16ga ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Length: 18.72 * Width: 23.09</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>17-D-6007-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>17-D-6007-02-(16ga ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Length: 13.72 * Width: 23.09</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>17-D-6025-04</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>17-D-6025-04-(16ga ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Length: 23.08 * Width: 18.71</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P13549-16</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P13549-16-(14gacr ANSI-61) - K48 - V5-R0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Length: 35.80 * Width: 21.17</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P13704-151</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P13704-151-(12gacr ANSI-61) - K47 - V4-R3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Length: 91.08 * Width: 17.70</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P13704-152</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P13704-152-(12gacr ANSI-61) - K47 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Length: 91.08 * Width: 22.70</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P17690-17</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P17690-17-(14gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Length: 35.80 * Width: 21.17</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P19495-01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>P19495-01-(12gacr ANSI-61) - K47 - V0-R3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Length: 29.70 * Width: 13.58</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P19500-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P19500-16-(14gacr ANSI-61) - K48 - V3-R0</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Length: 43.79 * Width: 21.17</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PP12535-01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PP12535-01-(12gacr ANSI-61) - K47 - V1-R3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Length: 35.70 * Width: 21.08</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PP1510-02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DEFINER NOMBRE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Length: 8.71 * Width: 36.08</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PP19152-021</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Length: 21.80 * Width: 35.70</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PP19152-031</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Length: 21.80 * Width: 35.70</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PP21340-02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>DEFINER NOMBRE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Length: 16.03 * Width: 17.48</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PP21341-12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DEFINER NOMBRE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: 17.26</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PP22120-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PP22120-01-(16ga ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: 17.23</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PP22121-02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PP22121-02-(16ga ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: 26.01</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PP7517-10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PP7517-10-(16ga ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Length: 36.07 * Width: 31.20</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PP7533-05</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PP7533-05-(16ga ANSI-61) - K - V2-R0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Length: 11.41 * Width: 13.75</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PP9247</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PP9247-(14gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Length: 14.99 * Width: 13.02</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PP21340-03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PP21340-03-(16ga ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Length: 16.970 * Width: 15.000</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>12-D-6106-08</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>12-D-6106-08-(16ga ANSI-61) - K48 - V7-R0</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Length: 42.810 * Width: 9.940</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>12-D-6091-06</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>12-D-6091-06-(16ga ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Length: 29.94 * Width: 28.81</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>12-D-6085-06</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>12-D-6085-06-(16ga ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Length: 34.81 * Width: 12.44</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P19504-09</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P19504-09-(16ga ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Length: 28.81 * Width: 4.940</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>12-D-6348-12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12-D-6348-12-(16ga ANSI-61) - K48 - V12-R0</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Length: 34.810 * Width: 29.940</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>12-D-6106-07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>12-D-6106-07-(16ga ANSI-61) - K48 - V7-R0</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Length: 34.82 * Width: 9.94</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12-D-6091-04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>12-D-6091-04-(16ga ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Length: 29.940 * Width: 21.810</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>P6298-051</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DEFINIR NOMBRE </t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>DEFINER NOMBRE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>Length: 29.940 * Width: 28.810</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,66 +527,66 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P13704-091</t>
+          <t>11-A-6014-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P13704-091-(14gacr ANSI-61) - K48 - V5-R0</t>
+          <t>11-A-6014-01-(16ga ANSI-61) - K48 - V5-R0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Length: 28.81 * Width: 24.88</t>
+          <t>Length: 34.81 * Width: 12.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P13704-091</t>
+          <t>11-a-6004-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P13704-091-(14gacr ANSI-61) - K48 - V5-R0</t>
+          <t>11-A-6004-01-(16ga ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Length: 28.81 * Width: 24.88</t>
+          <t>Length: 19.00 * Width: 3.50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI 61</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11-A-6014-01</t>
+          <t>12-6010-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11-A-6014-01-(16ga ANSI-61) - K48 - V5-R0</t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Length: 34.81 * Width: 12.44</t>
+          <t>Length: 19.00 * Width: 2.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -608,12 +608,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11-a-6004-01</t>
+          <t>12-6010-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11-A-6004-01-(16ga ANSI-61) - K48 - V3-R0</t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 3.50</t>
+          <t>Length: 19.00 * Width: 6.01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -635,22 +635,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12-6010-01</t>
+          <t>12-A-6200-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>12-A-6200-02-(12gacr ANSI-61) - K47 - V4-R2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 2.26</t>
+          <t>Length: 29.70 * Width: 16.09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -662,22 +662,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12-6010-03</t>
+          <t>12-A-6359-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>12-A-6359-02-(12gacr ANSI-61) - K47 - V6-R3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 6.01</t>
+          <t>Length: 21.08 * Width: 35.70</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -689,22 +689,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12-A-6200-02</t>
+          <t>12-C-6017-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12-A-6200-02-(12gacr ANSI-61) - K47 - V4-R2</t>
+          <t>12-C-6017-01-(16ga ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Length: 29.70 * Width: 16.09</t>
+          <t>Length: 28.81 * Width: 7.44</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -716,22 +716,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12-A-6359-02</t>
+          <t>12-D-6047-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12-A-6359-02-(12gacr ANSI-61) - K47 - V6-R3</t>
+          <t>12-D-6047-03-(16ga ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Length: 21.08 * Width: 35.70</t>
+          <t>Length: 8.71 * Width: 44.08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12-C-6017-01</t>
+          <t>12-D-6063-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12-C-6017-01-(16ga ANSI-61) - K48 - V4-R0</t>
+          <t>12-D-6063-06-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Length: 28.81 * Width: 7.44</t>
+          <t>Length: 9.97 * Width: 36.09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -770,12 +770,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12-D-6047-03</t>
+          <t>12-D-6078-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12-D-6047-03-(16ga ANSI-61) - K48 - V4-R0</t>
+          <t>12-D-6078-05-(16ga ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 44.08</t>
+          <t>Length: 3.71 * Width: 30.08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -797,12 +797,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12-D-6063-06</t>
+          <t>12-D-6080-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12-D-6063-06-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6080-06-(16ga ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Length: 9.97 * Width: 36.09</t>
+          <t>Length: 6.22 * Width: 36.09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -824,12 +824,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12-D-6078-05</t>
+          <t>12-D-6081-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12-D-6078-05-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>12-D-6081-06-(16ga ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Length: 3.71 * Width: 30.08</t>
+          <t>Length: 7.47 * Width: 36.09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12-D-6080-06</t>
+          <t>12-D-6082-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12-D-6080-06-(16ga ANSI-61) - K48 - V4-R0</t>
+          <t>12-D-6082-05-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Length: 6.22 * Width: 36.09</t>
+          <t>Length: 8.71 * Width: 30.08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -878,12 +878,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12-D-6081-06</t>
+          <t>12-D-6082-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12-D-6081-06-(16ga ANSI-61) - K48 - V2-R0</t>
+          <t>12-D-6082-06-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Length: 7.47 * Width: 36.09</t>
+          <t>Length: 8.71 * Width: 36.08</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -905,12 +905,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12-D-6082-05</t>
+          <t>12-D-6083-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12-D-6082-05-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6083-06-(16ga ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 30.08</t>
+          <t>Length: 36.08 * Width: 11.21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12-D-6082-06</t>
+          <t>12-D-6088-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12-D-6082-06-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 36.08</t>
+          <t>Length: 36.08 * Width: 21.21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -959,12 +959,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12-D-6083-06</t>
+          <t>12-D-6091-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12-D-6083-06-(16ga ANSI-61) - K48 - V3-R0</t>
+          <t>12-D-6091-03-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Length: 36.08 * Width: 11.21</t>
+          <t>Length: 31.22 * Width: 18.09</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -986,12 +986,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>12-D-6088-08</t>
+          <t>12-D-6091-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>12-D-6091-08-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Length: 36.08 * Width: 21.21</t>
+          <t>Length: 31.22 * Width: 36.09</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1013,12 +1013,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>12-D-6091-03</t>
+          <t>12-c-6210-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12-D-6091-03-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Length: 31.22 * Width: 18.09</t>
+          <t>Length: 8.71 * Width: 36.08</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1040,12 +1040,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>12-D-6091-08</t>
+          <t>17-D-6004-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12-D-6091-08-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>17-D-6004-01-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Length: 31.22 * Width: 36.09</t>
+          <t>Length: 13.71 * Width: 23.09</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>12-c-6210-02</t>
+          <t>17-D-6004-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>17-D-6004-02-(16ga ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 36.08</t>
+          <t>Length: 31.16 * Width: 23.09</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17-D-6004-01</t>
+          <t>17-D-6007-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17-D-6004-01-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>17-D-6007-01-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Length: 13.71 * Width: 23.09</t>
+          <t>Length: 18.72 * Width: 23.09</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1121,12 +1121,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>17-D-6004-02</t>
+          <t>17-D-6007-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17-D-6004-02-(16ga ANSI-61) - K48 - V2-R0</t>
+          <t>17-D-6007-02-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Length: 31.16 * Width: 23.09</t>
+          <t>Length: 13.72 * Width: 23.09</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1148,12 +1148,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>17-D-6007-01</t>
+          <t>17-D-6025-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17-D-6007-01-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>17-D-6025-04-(16ga ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Length: 18.72 * Width: 23.09</t>
+          <t>Length: 23.08 * Width: 18.71</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1175,22 +1175,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>17-D-6007-02</t>
+          <t>P13549-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17-D-6007-02-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>P13549-16-(14gacr ANSI-61) - K48 - V5-R0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Length: 13.72 * Width: 23.09</t>
+          <t>Length: 35.80 * Width: 21.17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1202,22 +1202,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17-D-6025-04</t>
+          <t>P13704-151</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17-D-6025-04-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>P13704-151-(12gacr ANSI-61) - K47 - V4-R3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Length: 23.08 * Width: 18.71</t>
+          <t>Length: 91.08 * Width: 17.70</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1229,22 +1229,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P13549-16</t>
+          <t>P13704-152</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P13549-16-(14gacr ANSI-61) - K48 - V5-R0</t>
+          <t>P13704-152-(12gacr ANSI-61) - K47 - V0-R0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Length: 35.80 * Width: 21.17</t>
+          <t>Length: 91.08 * Width: 22.70</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1256,22 +1256,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>P13704-151</t>
+          <t>P17690-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>P13704-151-(12gacr ANSI-61) - K47 - V4-R3</t>
+          <t>P17690-17-(14gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Length: 91.08 * Width: 17.70</t>
+          <t>Length: 35.80 * Width: 21.17</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1283,12 +1283,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>P13704-152</t>
+          <t>P19495-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>P13704-152-(12gacr ANSI-61) - K47 - V0-R0</t>
+          <t>P19495-01-(12gacr ANSI-61) - K47 - V0-R3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Length: 91.08 * Width: 22.70</t>
+          <t>Length: 29.70 * Width: 13.58</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1310,12 +1310,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P17690-17</t>
+          <t>P19500-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>P17690-17-(14gacr ANSI-61) - K48 - V1-R0</t>
+          <t>P19500-16-(14gacr ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Length: 35.80 * Width: 21.17</t>
+          <t>Length: 43.79 * Width: 21.17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1337,12 +1337,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>P19495-01</t>
+          <t>PP12535-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>P19495-01-(12gacr ANSI-61) - K47 - V0-R3</t>
+          <t>PP12535-01-(12gacr ANSI-61) - K47 - V1-R3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Length: 29.70 * Width: 13.58</t>
+          <t>Length: 35.70 * Width: 21.08</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1364,22 +1364,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P19500-16</t>
+          <t>PP1510-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>P19500-16-(14gacr ANSI-61) - K48 - V3-R0</t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Length: 43.79 * Width: 21.17</t>
+          <t>Length: 8.71 * Width: 36.08</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PP12535-01</t>
+          <t>PP19152-021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PP12535-01-(12gacr ANSI-61) - K47 - V1-R3</t>
+          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Length: 35.70 * Width: 21.08</t>
+          <t>Length: 21.80 * Width: 35.70</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1418,22 +1418,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PP1510-02</t>
+          <t>PP19152-031</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 36.08</t>
+          <t>Length: 21.80 * Width: 35.70</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1445,22 +1445,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PP19152-021</t>
+          <t>PP21340-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Length: 21.80 * Width: 35.70</t>
+          <t>Length: 16.03 * Width: 17.48</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1472,22 +1472,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PP19152-031</t>
+          <t>PP21341-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Length: 21.80 * Width: 35.70</t>
+          <t>Length: 19.00 * Width: 17.26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PP21340-02</t>
+          <t>PP22120-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>PP22120-01-(16ga ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Length: 16.03 * Width: 17.48</t>
+          <t>Length: 19.00 * Width: 17.23</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1526,12 +1526,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PP21341-12</t>
+          <t>PP22121-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>PP22121-02-(16ga ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 17.26</t>
+          <t>Length: 19.00 * Width: 26.01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PP22120-01</t>
+          <t>PP7517-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PP22120-01-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>PP7517-10-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 17.23</t>
+          <t>Length: 36.07 * Width: 31.20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1580,12 +1580,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PP22121-02</t>
+          <t>PP7533-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PP22121-02-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>PP7533-05-(16ga ANSI-61) - K - V2-R0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 26.01</t>
+          <t>Length: 11.41 * Width: 13.75</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1607,22 +1607,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PP7517-10</t>
+          <t>PP9247</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PP7517-10-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>PP9247-(14gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Length: 36.07 * Width: 31.20</t>
+          <t>Length: 14.99 * Width: 13.02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1634,12 +1634,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PP7533-05</t>
+          <t>PP21340-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PP7533-05-(16ga ANSI-61) - K - V2-R0</t>
+          <t>PP21340-03-(16ga ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Length: 11.41 * Width: 13.75</t>
+          <t>Length: 16.970 * Width: 15.000</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1661,22 +1661,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PP9247</t>
+          <t>12-D-6106-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PP9247-(14gacr ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6106-08-(16ga ANSI-61) - K48 - V7-R0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Length: 14.99 * Width: 13.02</t>
+          <t>Length: 42.810 * Width: 9.940</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1688,12 +1688,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PP21340-03</t>
+          <t>12-D-6091-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PP21340-03-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>12-D-6091-06-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Length: 16.970 * Width: 15.000</t>
+          <t>Length: 29.94 * Width: 28.81</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1715,12 +1715,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>12-D-6106-08</t>
+          <t>12-D-6085-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12-D-6106-08-(16ga ANSI-61) - K48 - V7-R0</t>
+          <t>12-D-6085-06-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Length: 42.810 * Width: 9.940</t>
+          <t>Length: 34.81 * Width: 12.44</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1742,12 +1742,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>12-D-6091-06</t>
+          <t>P19504-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12-D-6091-06-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>P19504-09-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Length: 29.94 * Width: 28.81</t>
+          <t>Length: 28.81 * Width: 4.940</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1769,12 +1769,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12-D-6085-06</t>
+          <t>12-D-6348-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12-D-6085-06-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6348-12-(16ga ANSI-61) - K48 - V12-R0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Length: 34.81 * Width: 12.44</t>
+          <t>Length: 34.810 * Width: 29.940</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1796,12 +1796,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>P19504-09</t>
+          <t>12-D-6106-07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>P19504-09-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6106-07-(16ga ANSI-61) - K48 - V7-R0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Length: 28.81 * Width: 4.940</t>
+          <t>Length: 34.82 * Width: 9.94</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1823,12 +1823,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>12-D-6348-12</t>
+          <t>12-D-6091-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12-D-6348-12-(16ga ANSI-61) - K48 - V12-R0</t>
+          <t>12-D-6091-04-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Length: 34.810 * Width: 29.940</t>
+          <t>Length: 29.940 * Width: 21.810</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1850,12 +1850,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>12-D-6106-07</t>
+          <t>P6298-051</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12-D-6106-07-(16ga ANSI-61) - K48 - V7-R0</t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1865,64 +1865,10 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Length: 34.82 * Width: 9.94</t>
+          <t>Length: 29.940 * Width: 28.810</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
-        <is>
-          <t>ANSI 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>12-D-6091-04</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>12-D-6091-04-(16ga ANSI-61) - K48 - V1-R0</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Length: 29.940 * Width: 21.810</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>ANSI 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>P6298-051</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>DEFINER NOMBRE</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>16GACR</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Length: 29.940 * Width: 28.810</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
         <is>
           <t>ANSI 61</t>
         </is>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11-a-6004-01</t>
+          <t>11-A-6004-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>12-c-6210-02</t>
+          <t>12-C-6210-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1094,22 +1094,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17-D-6007-01</t>
+          <t>P13549-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17-D-6007-01-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>P13549-16-(14gacr ANSI-61) - K48 - V5-R0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Length: 18.72 * Width: 23.09</t>
+          <t>Length: 35.80 * Width: 21.17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1121,22 +1121,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>17-D-6007-02</t>
+          <t>P13704-151</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17-D-6007-02-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>P13704-151-(12gacr ANSI-61) - K47 - V4-R3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Length: 13.72 * Width: 23.09</t>
+          <t>Length: 91.08 * Width: 17.70</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1148,22 +1148,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>17-D-6025-04</t>
+          <t>P13704-152</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17-D-6025-04-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>P13704-152-(12gacr ANSI-61) - K47 - V0-R0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Length: 23.08 * Width: 18.71</t>
+          <t>Length: 91.08 * Width: 22.70</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P13549-16</t>
+          <t>P17690-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>P13549-16-(14gacr ANSI-61) - K48 - V5-R0</t>
+          <t>P17690-17-(14gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,12 +1202,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>P13704-151</t>
+          <t>P19495-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P13704-151-(12gacr ANSI-61) - K47 - V4-R3</t>
+          <t>P19495-01-(12gacr ANSI-61) - K47 - V0-R3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Length: 91.08 * Width: 17.70</t>
+          <t>Length: 29.70 * Width: 13.58</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1229,22 +1229,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P13704-152</t>
+          <t>P19500-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P13704-152-(12gacr ANSI-61) - K47 - V0-R0</t>
+          <t>P19500-16-(14gacr ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Length: 91.08 * Width: 22.70</t>
+          <t>Length: 43.79 * Width: 21.17</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1256,22 +1256,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>P17690-17</t>
+          <t>PP12535-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>P17690-17-(14gacr ANSI-61) - K48 - V1-R0</t>
+          <t>PP12535-01-(12gacr ANSI-61) - K47 - V1-R3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Length: 35.80 * Width: 21.17</t>
+          <t>Length: 35.70 * Width: 21.08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1283,22 +1283,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>P19495-01</t>
+          <t>PP1510-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>P19495-01-(12gacr ANSI-61) - K47 - V0-R3</t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Length: 29.70 * Width: 13.58</t>
+          <t>Length: 8.71 * Width: 36.08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1310,22 +1310,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P19500-16</t>
+          <t>PP19152-021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>P19500-16-(14gacr ANSI-61) - K48 - V3-R0</t>
+          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Length: 43.79 * Width: 21.17</t>
+          <t>Length: 21.80 * Width: 35.70</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1337,12 +1337,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PP12535-01</t>
+          <t>PP19152-031</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PP12535-01-(12gacr ANSI-61) - K47 - V1-R3</t>
+          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Length: 35.70 * Width: 21.08</t>
+          <t>Length: 21.80 * Width: 35.70</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PP1510-02</t>
+          <t>PP21340-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 36.08</t>
+          <t>Length: 16.03 * Width: 17.48</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1391,22 +1391,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PP19152-021</t>
+          <t>PP21341-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Length: 21.80 * Width: 35.70</t>
+          <t>Length: 19.00 * Width: 17.26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1418,22 +1418,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PP19152-031</t>
+          <t>PP22120-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
+          <t>PP22120-01-(16ga ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Length: 21.80 * Width: 35.70</t>
+          <t>Length: 19.00 * Width: 17.23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1445,12 +1445,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PP21340-02</t>
+          <t>PP22121-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>PP22121-02-(16ga ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Length: 16.03 * Width: 17.48</t>
+          <t>Length: 19.00 * Width: 26.01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1472,12 +1472,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PP21341-12</t>
+          <t>PP7517-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>PP7517-10-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 17.26</t>
+          <t>Length: 36.07 * Width: 31.20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PP22120-01</t>
+          <t>PP7533-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PP22120-01-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>PP7533-05-(16ga ANSI-61) - K - V2-R0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 17.23</t>
+          <t>Length: 11.41 * Width: 13.75</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1526,22 +1526,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PP22121-02</t>
+          <t>PP9247</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PP22121-02-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>PP9247-(14gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 26.01</t>
+          <t>Length: 14.99 * Width: 13.02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PP7517-10</t>
+          <t>PP21340-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PP7517-10-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>PP21340-03-(16ga ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Length: 36.07 * Width: 31.20</t>
+          <t>Length: 16.970 * Width: 15.000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1580,12 +1580,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PP7533-05</t>
+          <t>12-D-6106-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PP7533-05-(16ga ANSI-61) - K - V2-R0</t>
+          <t>12-D-6106-08-(16ga ANSI-61) - K48 - V7-R0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Length: 11.41 * Width: 13.75</t>
+          <t>Length: 42.810 * Width: 9.940</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1607,22 +1607,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PP9247</t>
+          <t>12-D-6091-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PP9247-(14gacr ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6091-06-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Length: 14.99 * Width: 13.02</t>
+          <t>Length: 29.94 * Width: 28.81</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1634,12 +1634,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PP21340-03</t>
+          <t>12-D-6085-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PP21340-03-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>12-D-6085-06-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Length: 16.970 * Width: 15.000</t>
+          <t>Length: 34.81 * Width: 12.44</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1661,12 +1661,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>12-D-6106-08</t>
+          <t>P19504-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12-D-6106-08-(16ga ANSI-61) - K48 - V7-R0</t>
+          <t>P19504-09-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Length: 42.810 * Width: 9.940</t>
+          <t>Length: 28.81 * Width: 4.940</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1688,12 +1688,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>12-D-6091-06</t>
+          <t>12-D-6348-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12-D-6091-06-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6348-12-(16ga ANSI-61) - K48 - V12-R0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Length: 29.94 * Width: 28.81</t>
+          <t>Length: 34.810 * Width: 29.940</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1715,12 +1715,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>12-D-6085-06</t>
+          <t>12-D-6106-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12-D-6085-06-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6106-07-(16ga ANSI-61) - K48 - V7-R0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Length: 34.81 * Width: 12.44</t>
+          <t>Length: 34.82 * Width: 9.94</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1742,12 +1742,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>P19504-09</t>
+          <t>12-D-6091-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>P19504-09-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6091-04-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Length: 28.81 * Width: 4.940</t>
+          <t>Length: 29.940 * Width: 21.810</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1769,12 +1769,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12-D-6348-12</t>
+          <t>P6298-051</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12-D-6348-12-(16ga ANSI-61) - K48 - V12-R0</t>
+          <t>DEFINER NOMBRE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Length: 34.810 * Width: 29.940</t>
+          <t>Length: 29.940 * Width: 28.810</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1796,12 +1796,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12-D-6106-07</t>
+          <t>17-D-6007-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12-D-6106-07-(16ga ANSI-61) - K48 - V7-R0</t>
+          <t>17-D-6007-01-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Length: 34.82 * Width: 9.94</t>
+          <t>Length: 18.72 * Width: 23.09</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1823,12 +1823,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>12-D-6091-04</t>
+          <t>17-D-6007-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12-D-6091-04-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>17-D-6007-02-(16ga ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Length: 29.940 * Width: 21.810</t>
+          <t>Length: 13.72 * Width: 23.09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1850,12 +1850,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>P6298-051</t>
+          <t>17-D-6025-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>17-D-6025-04-(16ga ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Length: 29.940 * Width: 28.810</t>
+          <t>Length: 23.08 * Width: 18.71</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11-A-6014-01-(16ga ANSI-61) - K48 - V5-R0</t>
+          <t>11-A-6014-01-(16GACR ANSI-61) - K48 - V5-R0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11-A-6004-01-(16ga ANSI-61) - K48 - V3-R0</t>
+          <t>11-A-6004-01-(16GACR ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12-C-6017-01-(16ga ANSI-61) - K48 - V4-R0</t>
+          <t>12-C-6017-01-(16GACR ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12-D-6047-03-(16ga ANSI-61) - K48 - V4-R0</t>
+          <t>12-D-6047-03-(16GACRANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12-D-6063-06-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6063-06-(16GACR ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12-D-6078-05-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>12-D-6078-05-(16GACR ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12-D-6080-06-(16ga ANSI-61) - K48 - V4-R0</t>
+          <t>12-D-6080-06-(16GACR ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12-D-6081-06-(16ga ANSI-61) - K48 - V2-R0</t>
+          <t>12-D-6081-06-(16GACR ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12-D-6082-05-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6082-05-(16GACR ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12-D-6082-06-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6082-06-(16GACR ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12-D-6083-06-(16ga ANSI-61) - K48 - V3-R0</t>
+          <t>12-D-6083-06-(16GACR ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12-D-6091-03-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6091-03-(16GACR ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12-D-6091-08-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6091-08-(16GACR ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17-D-6004-01-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>17-D-6004-01-(16GACR ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17-D-6004-02-(16ga ANSI-61) - K48 - V2-R0</t>
+          <t>17-D-6004-02-(16GACR ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11-A-6014-01-(16GACR ANSI-61) - K48 - V5-R0</t>
+          <t>11-A-6014-01-(16gacr ANSI-61) - K48 - V5-R0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11-A-6004-01-(16GACR ANSI-61) - K48 - V3-R0</t>
+          <t>11-A-6004-01-(16gacr ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12-C-6017-01-(16GACR ANSI-61) - K48 - V4-R0</t>
+          <t>12-C-6017-01-(16gacr ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12-D-6047-03-(16GACRANSI-61) - K48 - V4-R0</t>
+          <t>12-D-6047-03-(16gacr ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12-D-6063-06-(16GACR ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6063-06-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12-D-6078-05-(16GACR ANSI-61) - K48 - V0-R0</t>
+          <t>12-D-6078-05-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12-D-6080-06-(16GACR ANSI-61) - K48 - V4-R0</t>
+          <t>12-D-6080-06-(16gacr ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12-D-6081-06-(16GACR ANSI-61) - K48 - V2-R0</t>
+          <t>12-D-6081-06-(16gacr ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12-D-6082-05-(16GACR ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6082-05-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12-D-6082-06-(16GACR ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6082-06-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12-D-6083-06-(16GACR ANSI-61) - K48 - V3-R0</t>
+          <t>12-D-6083-06-(16gacr ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12-D-6091-03-(16GACR ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6091-03-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12-D-6091-08-(16GACR ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6091-08-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17-D-6004-01-(16GACR ANSI-61) - K48 - V1-R0</t>
+          <t>17-D-6004-01-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17-D-6004-02-(16GACR ANSI-61) - K48 - V2-R0</t>
+          <t>17-D-6004-02-(16gacr ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PP22120-01-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>PP22120-01-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PP22121-02-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>PP22121-02-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PP7517-10-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>PP7517-10-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PP7533-05-(16ga ANSI-61) - K - V2-R0</t>
+          <t>PP7533-05-(16gacr ANSI-61) - K - V2-R0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PP21340-03-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>PP21340-03-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12-D-6106-08-(16ga ANSI-61) - K48 - V7-R0</t>
+          <t>12-D-6106-08-(16gacr ANSI-61) - K48 - V7-R0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12-D-6091-06-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6091-06-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12-D-6085-06-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6085-06-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>P19504-09-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>P19504-09-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12-D-6348-12-(16ga ANSI-61) - K48 - V12-R0</t>
+          <t>12-D-6348-12-(16gacr ANSI-61) - K48 - V12-R0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12-D-6106-07-(16ga ANSI-61) - K48 - V7-R0</t>
+          <t>12-D-6106-07-(16gacr ANSI-61) - K48 - V7-R0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12-D-6091-04-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6091-04-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17-D-6007-01-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>17-D-6007-01-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17-D-6007-02-(16ga ANSI-61) - K48 - V1-R0</t>
+          <t>17-D-6007-02-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>17-D-6025-04-(16ga ANSI-61) - K48 - V0-R0</t>
+          <t>17-D-6025-04-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PP7533-05-(16gacr ANSI-61) - K - V2-R0</t>
+          <t>PP7533-05-(16gacr ANSI-61) - K00 - V2-R0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -581,22 +581,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12-6010-01</t>
+          <t>12-A-6200-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>12-A-6200-02-(12gacr ANSI-61) - K47 - V4-R2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 2.26</t>
+          <t>Length: 29.70 * Width: 16.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -608,22 +608,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12-6010-03</t>
+          <t>12-A-6359-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>12-A-6359-02-(12gacr ANSI-61) - K47 - V6-R3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 6.01</t>
+          <t>Length: 21.08 * Width: 35.70</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -635,22 +635,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12-A-6200-02</t>
+          <t>12-C-6017-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12-A-6200-02-(12gacr ANSI-61) - K47 - V4-R2</t>
+          <t>12-C-6017-01-(16gacr ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Length: 29.70 * Width: 16.09</t>
+          <t>Length: 28.81 * Width: 7.44</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -662,22 +662,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12-A-6359-02</t>
+          <t>12-D-6047-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12-A-6359-02-(12gacr ANSI-61) - K47 - V6-R3</t>
+          <t>12-D-6047-03-(16gacr ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Length: 21.08 * Width: 35.70</t>
+          <t>Length: 8.71 * Width: 44.08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -689,12 +689,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12-C-6017-01</t>
+          <t>12-D-6063-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12-C-6017-01-(16gacr ANSI-61) - K48 - V4-R0</t>
+          <t>12-D-6063-06-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Length: 28.81 * Width: 7.44</t>
+          <t>Length: 9.97 * Width: 36.09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -716,12 +716,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12-D-6047-03</t>
+          <t>12-D-6078-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12-D-6047-03-(16gacr ANSI-61) - K48 - V4-R0</t>
+          <t>12-D-6078-05-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 44.08</t>
+          <t>Length: 3.71 * Width: 30.08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12-D-6063-06</t>
+          <t>12-D-6080-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12-D-6063-06-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6080-06-(16gacr ANSI-61) - K48 - V4-R0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Length: 9.97 * Width: 36.09</t>
+          <t>Length: 6.22 * Width: 36.09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -770,12 +770,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12-D-6078-05</t>
+          <t>12-D-6081-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12-D-6078-05-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>12-D-6081-06-(16gacr ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Length: 3.71 * Width: 30.08</t>
+          <t>Length: 7.47 * Width: 36.09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -797,12 +797,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12-D-6080-06</t>
+          <t>12-D-6082-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12-D-6080-06-(16gacr ANSI-61) - K48 - V4-R0</t>
+          <t>12-D-6082-05-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Length: 6.22 * Width: 36.09</t>
+          <t>Length: 8.71 * Width: 30.08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -824,12 +824,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12-D-6081-06</t>
+          <t>12-D-6082-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12-D-6081-06-(16gacr ANSI-61) - K48 - V2-R0</t>
+          <t>12-D-6082-06-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Length: 7.47 * Width: 36.09</t>
+          <t>Length: 8.71 * Width: 36.08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12-D-6082-05</t>
+          <t>12-D-6083-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12-D-6082-05-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6083-06-(16gacr ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 30.08</t>
+          <t>Length: 36.08 * Width: 11.21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -878,12 +878,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12-D-6082-06</t>
+          <t>12-D-6091-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12-D-6082-06-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6091-03-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 36.08</t>
+          <t>Length: 31.22 * Width: 18.09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -905,12 +905,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12-D-6083-06</t>
+          <t>12-D-6091-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12-D-6083-06-(16gacr ANSI-61) - K48 - V3-R0</t>
+          <t>12-D-6091-08-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Length: 36.08 * Width: 11.21</t>
+          <t>Length: 31.22 * Width: 36.09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12-D-6088-08</t>
+          <t>17-D-6004-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>17-D-6004-01-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Length: 36.08 * Width: 21.21</t>
+          <t>Length: 13.71 * Width: 23.09</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -959,12 +959,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12-D-6091-03</t>
+          <t>17-D-6004-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12-D-6091-03-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>17-D-6004-02-(16gacr ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Length: 31.22 * Width: 18.09</t>
+          <t>Length: 31.16 * Width: 23.09</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -986,22 +986,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>12-D-6091-08</t>
+          <t>P13549-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12-D-6091-08-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>P13549-16-(14gacr ANSI-61) - K48 - V5-R0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Length: 31.22 * Width: 36.09</t>
+          <t>Length: 35.80 * Width: 21.17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1013,22 +1013,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>12-C-6210-02</t>
+          <t>P13704-151</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>P13704-151-(12gacr ANSI-61) - K47 - V4-R3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 36.08</t>
+          <t>Length: 91.08 * Width: 17.70</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1040,22 +1040,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>17-D-6004-01</t>
+          <t>P13704-152</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17-D-6004-01-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>P13704-152-(12gacr ANSI-61) - K47 - V0-R0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Length: 13.71 * Width: 23.09</t>
+          <t>Length: 91.08 * Width: 22.70</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1067,22 +1067,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>17-D-6004-02</t>
+          <t>P17690-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17-D-6004-02-(16gacr ANSI-61) - K48 - V2-R0</t>
+          <t>P17690-17-(14gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Length: 31.16 * Width: 23.09</t>
+          <t>Length: 35.80 * Width: 21.17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1094,22 +1094,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P13549-16</t>
+          <t>P19495-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>P13549-16-(14gacr ANSI-61) - K48 - V5-R0</t>
+          <t>P19495-01-(12gacr ANSI-61) - K47 - V0-R3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Length: 35.80 * Width: 21.17</t>
+          <t>Length: 29.70 * Width: 13.58</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1121,22 +1121,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P13704-151</t>
+          <t>P19500-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>P13704-151-(12gacr ANSI-61) - K47 - V4-R3</t>
+          <t>P19500-16-(14gacr ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Length: 91.08 * Width: 17.70</t>
+          <t>Length: 43.79 * Width: 21.17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1148,12 +1148,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P13704-152</t>
+          <t>PP12535-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>P13704-152-(12gacr ANSI-61) - K47 - V0-R0</t>
+          <t>PP12535-01-(12gacr ANSI-61) - K47 - V1-R3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Length: 91.08 * Width: 22.70</t>
+          <t>Length: 35.70 * Width: 21.08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1175,22 +1175,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P17690-17</t>
+          <t>PP19152-021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>P17690-17-(14gacr ANSI-61) - K48 - V1-R0</t>
+          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Length: 35.80 * Width: 21.17</t>
+          <t>Length: 21.80 * Width: 35.70</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1202,12 +1202,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>P19495-01</t>
+          <t>PP19152-031</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P19495-01-(12gacr ANSI-61) - K47 - V0-R3</t>
+          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Length: 29.70 * Width: 13.58</t>
+          <t>Length: 21.80 * Width: 35.70</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1229,22 +1229,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P19500-16</t>
+          <t>PP22120-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P19500-16-(14gacr ANSI-61) - K48 - V3-R0</t>
+          <t>PP22120-01-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Length: 43.79 * Width: 21.17</t>
+          <t>Length: 19.00 * Width: 17.23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1256,22 +1256,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PP12535-01</t>
+          <t>PP22121-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PP12535-01-(12gacr ANSI-61) - K47 - V1-R3</t>
+          <t>PP22121-02-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Length: 35.70 * Width: 21.08</t>
+          <t>Length: 19.00 * Width: 26.01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1283,12 +1283,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PP1510-02</t>
+          <t>PP7517-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>PP7517-10-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 36.08</t>
+          <t>Length: 36.07 * Width: 31.20</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1310,22 +1310,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PP19152-021</t>
+          <t>PP7533-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
+          <t>PP7533-05-(16gacr ANSI-61) - K00 - V2-R0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Length: 21.80 * Width: 35.70</t>
+          <t>Length: 11.41 * Width: 13.75</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1337,22 +1337,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PP19152-031</t>
+          <t>PP9247</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PP19152-021-(12gacr ANSI-61) - K47 - v1-R3</t>
+          <t>PP9247-(14gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Length: 21.80 * Width: 35.70</t>
+          <t>Length: 14.99 * Width: 13.02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1364,12 +1364,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PP21340-02</t>
+          <t>PP21340-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>PP21340-03-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Length: 16.03 * Width: 17.48</t>
+          <t>Length: 16.970 * Width: 15.000</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PP21341-12</t>
+          <t>12-D-6106-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>12-D-6106-08-(16gacr ANSI-61) - K48 - V7-R0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 17.26</t>
+          <t>Length: 42.810 * Width: 9.940</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1418,12 +1418,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PP22120-01</t>
+          <t>12-D-6091-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PP22120-01-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>12-D-6091-06-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 17.23</t>
+          <t>Length: 29.94 * Width: 28.81</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1445,12 +1445,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PP22121-02</t>
+          <t>12-D-6085-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PP22121-02-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>12-D-6085-06-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 26.01</t>
+          <t>Length: 34.81 * Width: 12.44</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1472,12 +1472,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PP7517-10</t>
+          <t>P19504-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PP7517-10-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>P19504-09-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Length: 36.07 * Width: 31.20</t>
+          <t>Length: 28.81 * Width: 4.940</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PP7533-05</t>
+          <t>12-D-6348-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PP7533-05-(16gacr ANSI-61) - K00 - V2-R0</t>
+          <t>12-D-6348-12-(16gacr ANSI-61) - K48 - V12-R0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Length: 11.41 * Width: 13.75</t>
+          <t>Length: 34.810 * Width: 29.940</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1526,22 +1526,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PP9247</t>
+          <t>12-D-6106-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PP9247-(14gacr ANSI-61) - K48 - V1-R0</t>
+          <t>12-D-6106-07-(16gacr ANSI-61) - K48 - V7-R0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Length: 14.99 * Width: 13.02</t>
+          <t>Length: 34.82 * Width: 9.94</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PP21340-03</t>
+          <t>12-D-6091-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PP21340-03-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>12-D-6091-04-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Length: 16.970 * Width: 15.000</t>
+          <t>Length: 29.940 * Width: 21.810</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1580,12 +1580,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12-D-6106-08</t>
+          <t>17-D-6007-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12-D-6106-08-(16gacr ANSI-61) - K48 - V7-R0</t>
+          <t>17-D-6007-01-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Length: 42.810 * Width: 9.940</t>
+          <t>Length: 18.72 * Width: 23.09</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1607,12 +1607,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>12-D-6091-06</t>
+          <t>17-D-6007-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12-D-6091-06-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>17-D-6007-02-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Length: 29.94 * Width: 28.81</t>
+          <t>Length: 13.72 * Width: 23.09</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1634,12 +1634,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>12-D-6085-06</t>
+          <t>17-D-6025-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12-D-6085-06-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>17-D-6025-04-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Length: 34.81 * Width: 12.44</t>
+          <t>Length: 23.08 * Width: 18.71</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1661,12 +1661,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>P19504-09</t>
+          <t>12-6010-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>P19504-09-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>12-6010-01-(16gacr ANSI-61) - K48 - V11-R0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1676,24 +1676,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Length: 28.81 * Width: 4.940</t>
+          <t>Length: 19.00 * Width: 2.26</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI61</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>12-D-6348-12</t>
+          <t>12-6010-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12-D-6348-12-(16gacr ANSI-61) - K48 - V12-R0</t>
+          <t>12-6010-03-(16gacr ANSI-61) - K48 - V11-R0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1703,24 +1703,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Length: 34.810 * Width: 29.940</t>
+          <t>Length: 19.00 * Width: 3.51</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI61</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>12-D-6106-07</t>
+          <t>12-D-6088-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12-D-6106-07-(16gacr ANSI-61) - K48 - V7-R0</t>
+          <t>12-D-6088-08-(16gacr ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1730,24 +1730,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Length: 34.82 * Width: 9.94</t>
+          <t>Length: 36.08 * Width: 21.21</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI61</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>12-D-6091-04</t>
+          <t>12-C-6210-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12-D-6091-04-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>12-C-6210-02-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1757,24 +1757,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Length: 29.940 * Width: 21.810</t>
+          <t>Length: 8.71* Width: 36.08</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI61</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>P6298-051</t>
+          <t>PP1510-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DEFINER NOMBRE</t>
+          <t>PP1510-02-(16gacr ANSI-61) - K48 - V5-R0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1784,24 +1784,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Length: 29.940 * Width: 28.810</t>
+          <t>Length: 8.71* Width: 36.08</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI61</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17-D-6007-01</t>
+          <t>PP21340-02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17-D-6007-01-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>PP21340-02-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1811,51 +1811,51 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Length: 18.72 * Width: 23.09</t>
+          <t>Length: 16.03* Width: 17.48</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI61</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17-D-6007-02</t>
+          <t>PP21341-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17-D-6007-02-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>PP21341-12-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Length: 13.72 * Width: 23.09</t>
+          <t>Length: 19.00* Width: 17.26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI61</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17-D-6025-04</t>
+          <t>P6298-051</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>17-D-6025-04-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>P6298-51-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Length: 23.08 * Width: 18.71</t>
+          <t>Length: 31.20 * Width: 30.07</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -1681,7 +1681,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1874,6 +1874,33 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PP22124-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PP22124-01-(16gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Length: 22.5 * Width: 16.97</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1901,6 +1901,33 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>11-D-3408-01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>11-D-3408-01-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Length: 2.0 * Width: 1.125</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1928,6 +1928,546 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>12-6010-02</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>12-6010-02-(16gacr ANSI-61) - K48 - V11-R0</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: 2.47</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>12-6010-09</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>12-6010-09-(16gacr ANSI-61) - K48 - V11-R0</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: 6.22</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>12-6010-10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>12-6010-10-(16gacr ANSI-61) - K48 - V11-R0</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: 8.72</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>12-6113-05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>12-6113-05-(12gacr ANSI-61) - K47 - V13-R2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Length: 29.70 * Width: 28.81</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>12-A-6199-02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>12-A-6199-02-(12gacr ANSI-61) - K47 - V3-R2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Length: 21.08 * Width: 34.81</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>12-A-6200-03</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>12-A-6200-03-(12gacr ANSI-61) - K47 - V4-R3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Length: 35.70 * Width: 34.81</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>12-C-6210-01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>12-C-6210-01-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Length: 8.71 * Width: 34.81</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>12-D-6033-05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>12-D-6033-05-(12gacr ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Length: 75.00 * Width: 3.37</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>12-D-6107-01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>12-D-6107-01-(16gacr ANSI-61) - K48 - V4-R1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Length: 31.21 * Width: 34.81</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P19500-20</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P19500-20-(12gacr ANSI-61) - K47 - V1-R3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Length: 43.70 * Width: 14.94</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P19500-25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P19500-25-(12gacr ANSI-61) - K47 - V0-R3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Length: 43.70 * Width: 14.94</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P19500-26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P19500-26-(12gacr ANSI-61) - K47 - V0-R3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Length: 43.70 * Width: 14.94</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>P20365-02</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P20365-02-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Length: 31.20* Width: 29.94</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PP14805-04</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PP14805-04-(12gacr ANSI-61) - K47 - V0-R3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Length: 43.70* Width: 17.44</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PP15509</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PP15509-(14gacr ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>14GACR</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Length: 35.80* Width: 19.94</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PP15536-02</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PP15536-02-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Length: 23.53* Width: 16.97</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PP17250-06</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PP17250-06-(12gacr ANSI-61) - K47 - V0-R3</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Length: 16.08* Width: 14.94</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PP19152-04</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PP19152-04-(12gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Length: 21.08* Width: 19.94</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PP21340-01</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PP21340-01-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Length: 11.03* Width: 17.48</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PP22121-01</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PP22121-01-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Length: 19.00* Width: 24.97</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ANSI 61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ANSI 61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,22 +1823,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PP21341-12</t>
+          <t>P6298-051</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PP21341-12-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>P6298-51-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Length: 19.00* Width: 17.26</t>
+          <t>Length: 31.20 * Width: 30.07</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1850,12 +1850,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>P6298-051</t>
+          <t>PP22124-01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>P6298-51-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>PP22124-01-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Length: 31.20 * Width: 30.07</t>
+          <t>Length: 22.5 * Width: 16.97</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1877,12 +1877,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PP22124-01</t>
+          <t>11-D-3408-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PP22124-01-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>11-D-3408-01-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Length: 22.5 * Width: 16.97</t>
+          <t>Length: 2.0 * Width: 1.125</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1904,12 +1904,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>11-D-3408-01</t>
+          <t>12-6010-02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11-D-3408-01-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>12-6010-02-(16gacr ANSI-61) - K48 - V11-R0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Length: 2.0 * Width: 1.125</t>
+          <t>Length: 19.00 * Width: 2.47</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>12-6010-02</t>
+          <t>12-6010-09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12-6010-02-(16gacr ANSI-61) - K48 - V11-R0</t>
+          <t>12-6010-09-(16gacr ANSI-61) - K48 - V11-R0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 2.47</t>
+          <t>Length: 19.00 * Width: 6.22</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1958,12 +1958,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>12-6010-09</t>
+          <t>12-6010-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12-6010-09-(16gacr ANSI-61) - K48 - V11-R0</t>
+          <t>12-6010-10-(16gacr ANSI-61) - K48 - V11-R0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 6.22</t>
+          <t>Length: 19.00 * Width: 8.72</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1985,22 +1985,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>12-6010-10</t>
+          <t>12-6113-05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12-6010-10-(16gacr ANSI-61) - K48 - V11-R0</t>
+          <t>12-6113-05-(12gacr ANSI-61) - K47 - V13-R2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 8.72</t>
+          <t>Length: 29.70 * Width: 28.81</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2012,12 +2012,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>12-6113-05</t>
+          <t>12-A-6199-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12-6113-05-(12gacr ANSI-61) - K47 - V13-R2</t>
+          <t>12-A-6199-02-(12gacr ANSI-61) - K47 - V3-R2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Length: 29.70 * Width: 28.81</t>
+          <t>Length: 21.08 * Width: 34.81</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2039,12 +2039,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>12-A-6199-02</t>
+          <t>12-A-6200-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12-A-6199-02-(12gacr ANSI-61) - K47 - V3-R2</t>
+          <t>12-A-6200-03-(12gacr ANSI-61) - K47 - V4-R3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Length: 21.08 * Width: 34.81</t>
+          <t>Length: 35.70 * Width: 34.81</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2066,22 +2066,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12-A-6200-03</t>
+          <t>12-C-6210-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12-A-6200-03-(12gacr ANSI-61) - K47 - V4-R3</t>
+          <t>12-C-6210-01-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Length: 35.70 * Width: 34.81</t>
+          <t>Length: 8.71 * Width: 34.81</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2093,22 +2093,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>12-C-6210-01</t>
+          <t>12-D-6033-05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12-C-6210-01-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>12-D-6033-05-(12gacr ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Length: 8.71 * Width: 34.81</t>
+          <t>Length: 75.00 * Width: 3.37</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2120,22 +2120,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>12-D-6033-05</t>
+          <t>12-D-6107-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12-D-6033-05-(12gacr ANSI-61) - K48 - V2-R0</t>
+          <t>12-D-6107-01-(16gacr ANSI-61) - K48 - V4-R1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Length: 75.00 * Width: 3.37</t>
+          <t>Length: 31.21 * Width: 34.81</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2147,22 +2147,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>12-D-6107-01</t>
+          <t>P19500-20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12-D-6107-01-(16gacr ANSI-61) - K48 - V4-R1</t>
+          <t>P19500-20-(12gacr ANSI-61) - K47 - V1-R3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Length: 31.21 * Width: 34.81</t>
+          <t>Length: 43.70 * Width: 14.94</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2174,12 +2174,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>P19500-20</t>
+          <t>P19500-25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>P19500-20-(12gacr ANSI-61) - K47 - V1-R3</t>
+          <t>P19500-25-(12gacr ANSI-61) - K47 - V0-R3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2201,12 +2201,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>P19500-25</t>
+          <t>P19500-26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>P19500-25-(12gacr ANSI-61) - K47 - V0-R3</t>
+          <t>P19500-26-(12gacr ANSI-61) - K47 - V0-R3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2228,22 +2228,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>P19500-26</t>
+          <t>P20365-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>P19500-26-(12gacr ANSI-61) - K47 - V0-R3</t>
+          <t>P20365-02-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Length: 43.70 * Width: 14.94</t>
+          <t>Length: 31.20* Width: 29.94</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2255,22 +2255,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>P20365-02</t>
+          <t>PP14805-04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>P20365-02-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>PP14805-04-(12gacr ANSI-61) - K47 - V0-R3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Length: 31.20* Width: 29.94</t>
+          <t>Length: 43.70* Width: 17.44</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2282,22 +2282,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PP14805-04</t>
+          <t>PP15509</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PP14805-04-(12gacr ANSI-61) - K47 - V0-R3</t>
+          <t>PP15509-(14gacr ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Length: 43.70* Width: 17.44</t>
+          <t>Length: 35.80* Width: 19.94</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2309,22 +2309,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PP15509</t>
+          <t>PP15536-02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PP15509-(14gacr ANSI-61) - K48 - V2-R0</t>
+          <t>PP15536-02-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>14GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Length: 35.80* Width: 19.94</t>
+          <t>Length: 23.53* Width: 16.97</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2336,22 +2336,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PP15536-02</t>
+          <t>PP17250-06</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PP15536-02-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>PP17250-06-(12gacr ANSI-61) - K47 - V0-R3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Length: 23.53* Width: 16.97</t>
+          <t>Length: 16.08* Width: 14.94</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2363,12 +2363,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PP17250-06</t>
+          <t>PP19152-04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PP17250-06-(12gacr ANSI-61) - K47 - V0-R3</t>
+          <t>PP19152-04-(12gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Length: 16.08* Width: 14.94</t>
+          <t>Length: 21.08* Width: 19.94</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2390,22 +2390,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PP19152-04</t>
+          <t>PP21340-01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PP19152-04-(12gacr ANSI-61) - K48 - V0-R0</t>
+          <t>PP21340-01-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Length: 21.08* Width: 19.94</t>
+          <t>Length: 11.03* Width: 17.48</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2417,12 +2417,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PP21340-01</t>
+          <t>PP22121-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PP21340-01-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>PP22121-01-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Length: 11.03* Width: 17.48</t>
+          <t>Length: 19.00* Width: 24.97</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2444,27 +2444,353 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PP22121-01</t>
+          <t>11-7761-02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PP22121-01-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>11-7761-02-(16gacr ANSI-61) - K0 - V3-R0</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>16GACR</t>
+          <t>16gacr</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Length: 19.00* Width: 24.97</t>
+          <t>Length: 9.50 * Width: .1.72</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>11-7761-03</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>11-7761-03-(16gacr ANSI-61) - K0 - V3-R0</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Length: 14.50 * Width: .1.72</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>11-7761-04</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>11-7761-04-(16gacr ANSI-61) - K0 - V3-R0</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Length: 22.00 * Width: .1.72</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>11-C-6119-01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>11-D-3402-01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>11-D-3402-01-(16gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: .6.22</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>11-D-3409-02</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>11-D-3409-02-(12gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Length: 5.15 * Width: 2.77</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>11-D-6192-01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>11-D-6193-01</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>12-6010-04</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>12-6010-04-(16gacr ANSI-61) - K48 - V11-R0</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Length: 19 * Width: 7.47</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>12-6355-02</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>12-6355-02-(16gacr ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Length: 11.03 * Width: 10</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>12-6355-03</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>12-D-6089-06</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>12-D-6089-06-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Length: 36.08 * Width: 34.81</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>17-D-6043-02</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>17-D-6047-01</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>P19500-17</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>P19500-18</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>P19500-19</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>P20255-02</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PP21341-12</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PP21341-12-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: 16.22</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -2525,33 +2525,49 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11-C-6119-01</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+          <t>11-D-3402-01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>11-D-3402-01-(16gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: .6.22</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11-D-3402-01</t>
+          <t>11-D-3409-02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11-D-3402-01-(16gacr ANSI-61) - K48 - V1-R0</t>
+          <t>11-D-3409-02-(12gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>12gacr</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: .6.22</t>
+          <t>Length: 5.15 * Width: 2.77</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2563,22 +2579,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11-D-3409-02</t>
+          <t>12-6010-04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>11-D-3409-02-(12gacr ANSI-61) - K48 - V1-R0</t>
+          <t>12-6010-04-(16gacr ANSI-61) - K48 - V11-R0</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>16gacr</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Length: 5.15 * Width: 2.77</t>
+          <t>Length: 19 * Width: 7.47</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2590,34 +2606,66 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11-D-6192-01</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+          <t>12-6355-02</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>12-6355-02-(16gacr ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Length: 11.03 * Width: 10</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11-D-6193-01</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+          <t>12-D-6089-06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>12-D-6089-06-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Length: 36.08 * Width: 34.81</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>12-6010-04</t>
+          <t>PP21341-12</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12-6010-04-(16gacr ANSI-61) - K48 - V11-R0</t>
+          <t>PP21341-12-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2627,7 +2675,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Length: 19 * Width: 7.47</t>
+          <t>Length: 19.00 * Width: 16.22</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2639,158 +2687,270 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>12-6355-02</t>
+          <t>11-C-6119-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12-6355-02-(16gacr ANSI-61) - K48 - V2-R0</t>
+          <t>11-C-6119-01-(12gacr Ansi61) - K48 - V1  R0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Length: 11.03 * Width: 10</t>
+          <t>Length: 90.00 * Width: 2.20</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>12-6355-03</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+          <t>11-D-6192-01</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>11-D-6192-01-(16gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: 4.97</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>12-D-6089-06</t>
+          <t>11-D-6193-01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12-D-6089-06-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>11-D-6193-01-(16gacr ANSI-61) - K0 - V1-R0</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Length: 36.08 * Width: 34.81</t>
+          <t>Length: 4.97 * Width: 4.44</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>17-D-6043-02</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+          <t>12-6355-03</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>12-6355-03-(16gacr ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Length: 16.03 * Width: 15.00</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>17-D-6047-01</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+          <t>17-D-6043-02</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>17-D-6043-02-(16gacr ANSI-61) - K48 - V3-R1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: 6.22</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>P19500-17</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+          <t>17-D-6047-01</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>17-D-6047-01-(16gacr ANSI-61) - K0 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Length: 5.40 * Width: 5.90</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>P19500-18</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+          <t>P19500-17</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>P19500-17-(12gacr ANSI-61) - K47 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Length: 43.70 * Width: 14.94</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>P19500-19</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+          <t>P19500-18</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>P19500-18-(12gacr ANSI-61) - K47 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Length: 43.70 * Width: 14.94</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>P20255-02</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+          <t>P19500-19</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>P19500-19-(12gacr ANSI-61) - K47 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>12GACR</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Length: 43.70 * Width: 14.94</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PP21341-12</t>
+          <t>P20255-02</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PP21341-12-(16gacr ANSI-61) - K48 - V0-R0</t>
+          <t>P20255-02-(12gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Length: 19.00 * Width: 16.22</t>
+          <t>Length: 29.70 * Width: 12.44</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2954,6 +2954,168 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>11-6463-01</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>11-6463-01-(12gacr ANSI-61) - K61 - V6-R0</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Length: 10.75 * Width: 2.50</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>11-8232-01</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>11-8232-01-(12gacr ANSI-61) - K61 - V4-R0</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Length: 3.37 * Width: 2.63</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>12-6010-05</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>12-6010-05-(16gacr ANSI-61) - K48 - V11-R0</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Length: 19.00 * Width: 11.01</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>12-D-6106-06</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>12-D-6106-06-(16gacr ANSI-61) - K48 - V7-R0</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Length: 11.21 * Width: 30.08</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>12-D-6108-01</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>12-D-6108-01-(14gacr ANSI-61) - K48 - V3-R0</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>14gacr</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Length: 31.16 * Width: 44.08</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>16-6047-01</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>16-6047-01-(12gacr ANSI-61) - K56 - V9-R0</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Length: 29.00 * Width: 3.20</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3116,6 +3116,33 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PP14023-06</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PP14023-06-(16gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Length: 16.030 * Width: 17.48</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3143,6 +3143,87 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>12-C-6211-08</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>12-C-6211-08-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Length: 11.21 * Width: 44.08</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>12-D-6086-07</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>12-D-6086-07-(16gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Length: 42.81 * Width: 16.21</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>12-D-6099-13</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>12-D-6099-13-(14gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>14gacr</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Length: 31.16 * Width: 42.81</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3224,6 +3224,519 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>11-A-6015-01</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>11-A-6015-01-(16gacr ANSI-61) - K48 - V3-R0</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Length: 44.94 * Width: 16.81</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>11-A-6016-01</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>11-A-6016-01-(16gacr ANSI-61) - K48 - V5-R0</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Length: 46.20 * Width: 24.81</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>12-C-6210-03</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>12-C-6210-03-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Length: 7.44* Width: 42.81</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>12-C-6211-07</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>12-C-6211-07-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Length: 9.94* Width: 34.81</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>12-D-6080-07</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>12-D-6080-07-(16gacr ANSI-61) - K48 - V4-R0</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Length: 4.94* Width: 42.81</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>P14345-22</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>P14345-22-(14gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>14gacr</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Length: 42.81* Width: 22.38</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>P19657-01</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>P19657-01-(12gacr ANSI-61) - K61 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Length: 47.12* Width: 4.50</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>P19657-24</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>P19657-24-(16gacr ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Length: 54.13* Width: 42.44</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>P19657-25</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>P19657-25-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Length: 47.44* Width: 14.81</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>P19657-26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>P19657-26-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Length: 47.44* Width: 16.81</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>P19671-05</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>P19671-05-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Length: 17.44* Width: 42.81</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>P20321S-08-01</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>P20321S-08-01-(14gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>14gacr</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Length: 34.81* Width: 19.94</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>P20325-23</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>P20325-23-(12gacr ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Length: 42.81* Width: 14.94</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>P20336-01</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>P20336-01-(12gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Length: 34.81* Width: 19.94</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>PP10315-01</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PP10315-01-(14gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>14gacr</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Length: 29.94* Width: 42.81</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>PP13629-12</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PP13629-12-(16gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Length: 10.00* Width: 16.97</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>PP17250-05</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PP17250-05-(12gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Length: 14.94* Width: 28.81</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>PP19380-03</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PP19380-03-(12gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Length: 42.81* Width: 9.94</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>PP22114-06</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PP22114-06-(12gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Length: 34.81* Width: 14.94</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>14gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3737,6 +3737,33 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>P19660-14</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>P19660-14-(12gacr ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Length: 42.81 * Width:19.44</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -3750,7 +3750,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3764,6 +3764,33 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PP19568-02</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PP19568-02-(16gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>16GACR</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Length: 16.22 * Width: 36.09</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3791,6 +3791,168 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>12-D-6101-01</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>12-D-6101-01-(125Al ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>125Al</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Length: 29.94 * Width: 34.87</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>12-D-6101-02</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>12-D-6101-02-(125Al ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>125Al</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Length: 29.94 * Width: 42.87</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>12-D-6101-05</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>12-D-6101-05-(125Al ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>125Al</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Length: 29.94 * Width: 16.87</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>12-D-6101-06</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>12-D-6101-06-(125Al ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>125Al</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Length: 29.94 * Width: 18.87</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>12-D-7930-01</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>12-D-7930-01-(125Al ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>125Al</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Length: 29.94 * Width: 34.87</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>12-D-7930-02</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>12-D-7930-02-(125Al ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>125Al</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Length: 29.94 * Width: 42.87</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3953,6 +3953,87 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>12-D-6085-07</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>12-D-6085-07-(16gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>16gacr</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Length: 12.44 * Width: 42.81</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>P20330-02</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>P20330-02-(12gacr ANSI-61) - K48 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Length: 74.94 * Width: 28.81</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PP8655</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PP8655-(12gacr ANSI-61) - K48 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Length: 31.87 * Width: 23.37</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>125Al</t>
+          <t>125AL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>125Al</t>
+          <t>125AL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>125Al</t>
+          <t>125AL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>125Al</t>
+          <t>125AL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>125Al</t>
+          <t>125AL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>125Al</t>
+          <t>125AL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>16gacr</t>
+          <t>16GACR</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4034,6 +4034,1041 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>P20321-12</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>P20321-12-(10Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>10Ga</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>P20346-04</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>P20346-04-(10Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>10Ga</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PP14112-19</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PP14112-19-(10Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>10Ga</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>P20321-13</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>P20321-13-(10Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>10Ga</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>11-A-6037-01</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>11-A-6037-01-(12Ga Galv) - K30 - V7-R0</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>11-D-6165-01</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>11-D-6165-01-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>P20321-15-11</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>P20321-15-11-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>P20321-15-12</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>P20321-15-12-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>P20512-08</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>P20512-08-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>P20512-09</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>P20512-09-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>13-D-6196-01</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>13-D-6196-01-(12Ga Galv) - K30 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>P20512-18</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>P20512-18-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>13-D-6195-01</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>13-D-6195-01-(12Ga Galv) - K30 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>P20512-06</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>P20512-06-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>P20512-07</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>P20512-07-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>P17311-17</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>P17311-17-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>P20321-21</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>P20321-21-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PP20205-121</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PP20205-121-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>11-A-6030-01</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>11-A-6030-01-(12Ga Galv) - K30 - V4-R0</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PP20204-06</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PP20204-06-(12Ga Galv) - K30 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>PP20203-06</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PP20203-06-(12Ga Galv) - K30 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PP20205-061</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PP20205-061-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>P20153S-04</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>P20153S-04-(14Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>14Ga</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>P20321S-05</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>P20321S-05-(14Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>14Ga</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>P20321S-06</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>P20321S-06-(14Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>14Ga</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>12-6383-01</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>12-6383-01-(14Ga Galv) - K30 - V9-R0</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>14Ga</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>12-D-6015-05</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>12-D-6015-05-(10Ga Galv) - K30 - V5-R0</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>10Ga</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>12-D-6017-02</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>12-D-6017-02-(10Ga Galv) - K30 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>10Ga</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>12-D-6234-08</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>12-D-6234-08-(12Ga Galv) - K30 - V3-R0</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>12-D-6234-06</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>12-D-6234-06-(12Ga Galv) - K30 - V3-R0</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PP20204-12</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PP20204-12-(12Ga Galv) - K30 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>PP20204-13</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PP20204-13-(12Ga Galv) - K30 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>PP20203-12</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>PP20203-12-(12Ga Galv) - K30 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>PP20203-13</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PP20203-13-(12Ga Galv) - K30 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>PP13949-04</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PP13949-04-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>PP13949-09</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PP13949-09-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>PP20205-131</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PP20205-131-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>PP20205-132</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PP20205-132-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>12-6267-01</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>12-6267-01-(12Ga Galv) - K30 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PP13949-10</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PP13949-10-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PP13949-08</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PP13949-08-(12Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>96-6183-01</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>96-6183-01-(14Ga Galv) - K30 - V5-R0</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>14Ga</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>96-6183-02</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>96-6183-02-(14Ga Galv) - K30 - V5-R0</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>14Ga</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>P19663-24</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>P19663-24-(14Ga ) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>14Ga</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>12-6265-01</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>12-6265-01-(14Ga ) - K30 - V8-R0</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>14Ga</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -4047,13 +4047,13 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>10Ga</t>
+          <t>10GA</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4070,13 +4070,13 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>10Ga</t>
+          <t>10GA</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4093,13 +4093,13 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>10Ga</t>
+          <t>10GA</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4116,13 +4116,13 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>10Ga</t>
+          <t>10GA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4139,13 +4139,13 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4185,13 +4185,13 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4208,13 +4208,13 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4254,13 +4254,13 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4277,13 +4277,13 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4300,13 +4300,13 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4323,13 +4323,13 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4346,13 +4346,13 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>14Ga</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>14Ga</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>14Ga</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>14Ga</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>10Ga</t>
+          <t>10GA</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>10Ga</t>
+          <t>10GA</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>14Ga</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>14Ga</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>14Ga</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>14Ga</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4444,7 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4674,7 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4789,7 +4789,7 @@
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4812,7 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4835,7 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4973,7 @@
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -5065,7 +5065,7 @@
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5069,6 +5069,33 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>12-D-6234-10</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>12-D-6234-10-(12Ga Galv ) - K30 - V3-R0</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>12Ga</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Length: 40.50 * Width: 2.79</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -5082,7 +5082,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>12Ga</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -5092,7 +5092,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E180"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5096,6 +5096,33 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>P20325-25</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>P20325-25-(12ga Galv) - K0 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>12Galv</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Length: 4.62 * Width: 9.63</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -5109,7 +5109,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>12Galv</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5123,6 +5123,60 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>PP22114-05</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PP22114-05-(12gacr ANSI-61) - K48 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>12gacr</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Length: 34.81 * Width: 14.94</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>ANSI61</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>PP7517-01</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PP7517-01-(16ga GALV ) - K0 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>16Ga</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Length: 33.00 * Width: 0.94</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -5136,7 +5136,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>12gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>16Ga</t>
+          <t>16GA</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E183"/>
+  <dimension ref="A1:E184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5099,81 +5099,108 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>P20325-25</t>
+          <t>PP22114-05</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>P20325-25-(12ga Galv) - K0 - V0-R0</t>
+          <t>PP22114-05-(12gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>12GA</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Length: 4.62 * Width: 9.63</t>
+          <t>Length: 34.81 * Width: 14.94</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Galvanizado</t>
+          <t>Ansi 61</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PP22114-05</t>
+          <t>PP7517-01</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PP22114-05-(12gacr ANSI-61) - K48 - V0-R0</t>
+          <t>PP7517-01-(16ga GALV ) - K0 - V1-R0</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>12GACR</t>
+          <t>16GA</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Length: 34.81 * Width: 14.94</t>
+          <t>Length: 33.00 * Width: 0.94</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ansi 61</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PP7517-01</t>
+          <t>P20325-25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PP7517-01-(16ga GALV ) - K0 - V1-R0</t>
+          <t>P20325-25-(12ga Galv) - K0 - V0-R0</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>16GA</t>
+          <t>12Galv</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Length: 33.00 * Width: 0.94</t>
+          <t>Length: 4.62 * Width: 9.63</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Galvanizado</t>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>P20325-24</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>P20325-24-(10ga Galv ) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>10Galv</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Length: 61.19 * Width: 5.38</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Galv</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -5163,7 +5163,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>12Galv</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>10Galv</t>
+          <t>10GA</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5204,6 +5204,33 @@
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>P14734-10</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>P14734-10-(12ga GALV) - K30 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>12Galv</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Length: 38.28 * Width: 4.74</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -5217,7 +5217,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>12Galv</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Galvanizado</t>
         </is>
       </c>
     </row>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="641">
   <si>
     <t>SKU</t>
   </si>
@@ -1543,13 +1543,7 @@
     <t>Galvanizado</t>
   </si>
   <si>
-    <t>CLI-11-B-9016-01</t>
-  </si>
-  <si>
-    <t>CLI-P13704-101</t>
-  </si>
-  <si>
-    <t>CLI-P13704-091</t>
+    <t>ISSIV00099</t>
   </si>
   <si>
     <t>SWB00319</t>
@@ -1558,541 +1552,391 @@
     <t>SWB01125</t>
   </si>
   <si>
-    <t>CLI-12-A-6200-02</t>
-  </si>
-  <si>
-    <t>CLI-12-A-6359-02</t>
-  </si>
-  <si>
-    <t>CLI-12-C-6017-01</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6047-03</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6063-06</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6078-05</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6080-06</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6081-06</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6082-05</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6082-06</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6083-06</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6091-03</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6091-08</t>
-  </si>
-  <si>
-    <t>CLI-17-D-6004-01</t>
-  </si>
-  <si>
-    <t>CLI-17-D-6004-02</t>
-  </si>
-  <si>
-    <t>CLI-P13549-16</t>
-  </si>
-  <si>
-    <t>CLI-P13704-151</t>
-  </si>
-  <si>
-    <t>CLI-P13704-152</t>
-  </si>
-  <si>
-    <t>CLI-P17690-17</t>
-  </si>
-  <si>
-    <t>CLI-P19495-01</t>
-  </si>
-  <si>
-    <t>CLI-P19500-16</t>
-  </si>
-  <si>
-    <t>CLI-PP12535-01</t>
-  </si>
-  <si>
-    <t>CLI-PP19152-021</t>
-  </si>
-  <si>
-    <t>CLI-PP19152-031</t>
-  </si>
-  <si>
-    <t>CLI-PP22120-01</t>
-  </si>
-  <si>
-    <t>CLI-PP22121-02</t>
-  </si>
-  <si>
-    <t>CLI-PP7517-10</t>
-  </si>
-  <si>
-    <t>CLI-PP7533-05</t>
-  </si>
-  <si>
-    <t>CLI-PP9247</t>
-  </si>
-  <si>
-    <t>CLI-PP21340-03</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6106-08</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6091-06</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6085-06</t>
-  </si>
-  <si>
-    <t>CLI-P19504-09</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6348-12</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6106-07</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6091-04</t>
-  </si>
-  <si>
-    <t>CLI-17-D-6007-01</t>
-  </si>
-  <si>
-    <t>CLI-17-D-6007-02</t>
-  </si>
-  <si>
-    <t>CLI-17-D-6025-04</t>
-  </si>
-  <si>
-    <t>CLI-12-6010-01</t>
-  </si>
-  <si>
-    <t>CLI-12-6010-03</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6088-08</t>
-  </si>
-  <si>
-    <t>CLI-12-C-6210-02</t>
-  </si>
-  <si>
-    <t>CLI-PP1510-02</t>
-  </si>
-  <si>
-    <t>CLI-PP21340-02</t>
-  </si>
-  <si>
-    <t>CLI-P6298-051</t>
-  </si>
-  <si>
-    <t>CLI-PP22124-01</t>
-  </si>
-  <si>
-    <t>CLI-11-D-3408-01</t>
-  </si>
-  <si>
-    <t>CLI-12-6010-02</t>
-  </si>
-  <si>
-    <t>CLI-12-6010-09</t>
-  </si>
-  <si>
-    <t>CLI-12-6010-10</t>
-  </si>
-  <si>
-    <t>CLI-12-6113-05</t>
-  </si>
-  <si>
-    <t>CLI-12-A-6199-02</t>
-  </si>
-  <si>
-    <t>CLI-12-A-6200-03</t>
-  </si>
-  <si>
-    <t>CLI-12-C-6210-01</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6033-05</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6107-01</t>
-  </si>
-  <si>
-    <t>CLI-P19500-20</t>
-  </si>
-  <si>
-    <t>CLI-P19500-25</t>
-  </si>
-  <si>
-    <t>CLI-P19500-26</t>
-  </si>
-  <si>
-    <t>CLI-P20365-02</t>
-  </si>
-  <si>
-    <t>CLI-PP14805-04</t>
-  </si>
-  <si>
-    <t>CLI-PP15509</t>
-  </si>
-  <si>
-    <t>CLI-PP15536-02</t>
-  </si>
-  <si>
-    <t>CLI-PP17250-06</t>
-  </si>
-  <si>
-    <t>CLI-PP19152-04</t>
-  </si>
-  <si>
-    <t>CLI-PP21340-01</t>
-  </si>
-  <si>
-    <t>CLI-PP22121-01</t>
-  </si>
-  <si>
-    <t>CLI-11-7761-02</t>
-  </si>
-  <si>
-    <t>CLI-11-7761-03</t>
-  </si>
-  <si>
-    <t>CLI-11-7761-04</t>
+    <t>SWB00467</t>
+  </si>
+  <si>
+    <t>SWB00468</t>
+  </si>
+  <si>
+    <t>SWB00469</t>
+  </si>
+  <si>
+    <t>SWB00471</t>
+  </si>
+  <si>
+    <t>SWB00472</t>
+  </si>
+  <si>
+    <t>SWB00856</t>
+  </si>
+  <si>
+    <t>SWB00053</t>
+  </si>
+  <si>
+    <t>SWB00866</t>
+  </si>
+  <si>
+    <t>SWB00052</t>
+  </si>
+  <si>
+    <t>SWB00847</t>
+  </si>
+  <si>
+    <t>SWB00585</t>
+  </si>
+  <si>
+    <t>SWB00858</t>
+  </si>
+  <si>
+    <t>SWB00656</t>
+  </si>
+  <si>
+    <t>SWB00904</t>
+  </si>
+  <si>
+    <t>SWB01773</t>
+  </si>
+  <si>
+    <t>SWB01377</t>
+  </si>
+  <si>
+    <t>SWB01241</t>
+  </si>
+  <si>
+    <t>SWB00481</t>
+  </si>
+  <si>
+    <t>SWB00321</t>
+  </si>
+  <si>
+    <t>SWB00496</t>
+  </si>
+  <si>
+    <t>SWB00480</t>
+  </si>
+  <si>
+    <t>SWB00475</t>
+  </si>
+  <si>
+    <t>SWB00047</t>
+  </si>
+  <si>
+    <t>SWB00857</t>
+  </si>
+  <si>
+    <t>SWB01329</t>
+  </si>
+  <si>
+    <t>SWB01359</t>
+  </si>
+  <si>
+    <t>SWB00436</t>
+  </si>
+  <si>
+    <t>SWB00438</t>
+  </si>
+  <si>
+    <t>SWB01362</t>
+  </si>
+  <si>
+    <t>SWB01130</t>
+  </si>
+  <si>
+    <t>SWB00320</t>
+  </si>
+  <si>
+    <t>SWB00660</t>
+  </si>
+  <si>
+    <t>SWB00685</t>
+  </si>
+  <si>
+    <t>SWB00688</t>
+  </si>
+  <si>
+    <t>SWB01680</t>
+  </si>
+  <si>
+    <t>SWB01315</t>
+  </si>
+  <si>
+    <t>SWB01316</t>
+  </si>
+  <si>
+    <t>SWB01314</t>
+  </si>
+  <si>
+    <t>SWB01333</t>
   </si>
   <si>
     <t>SWB01126</t>
   </si>
   <si>
-    <t>CLI-11-D-3409-02</t>
-  </si>
-  <si>
     <t>SWB01260</t>
   </si>
   <si>
     <t>SWB01407</t>
   </si>
   <si>
-    <t>CLI-12-D-6089-06</t>
-  </si>
-  <si>
-    <t>CLI-PP21341-12</t>
-  </si>
-  <si>
-    <t>CLI-11-C-6119-01</t>
-  </si>
-  <si>
-    <t>CLI-11-D-6192-01</t>
-  </si>
-  <si>
-    <t>CLI-11-D-6193-01</t>
-  </si>
-  <si>
-    <t>CLI-12-6355-03</t>
-  </si>
-  <si>
-    <t>CLI-17-D-6043-02</t>
-  </si>
-  <si>
-    <t>CLI-17-D-6047-01</t>
-  </si>
-  <si>
-    <t>CLI-P19500-17</t>
-  </si>
-  <si>
-    <t>CLI-P19500-18</t>
-  </si>
-  <si>
-    <t>CLI-P19500-19</t>
-  </si>
-  <si>
-    <t>CLI-P20255-02</t>
-  </si>
-  <si>
-    <t>CLI-11-6463-01</t>
-  </si>
-  <si>
-    <t>CLI-11-8232-01</t>
-  </si>
-  <si>
-    <t>CLI-12-6010-05</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6106-06</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6108-01</t>
-  </si>
-  <si>
-    <t>CLI-16-6047-01</t>
-  </si>
-  <si>
-    <t>CLI-PP14023-06</t>
-  </si>
-  <si>
-    <t>CLI-12-C-6211-08</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6086-07</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6099-13</t>
-  </si>
-  <si>
-    <t>CLI-11-A-6015-01</t>
+    <t>SWB01313</t>
+  </si>
+  <si>
+    <t>SWB01134</t>
+  </si>
+  <si>
+    <t>SWB00657</t>
+  </si>
+  <si>
+    <t>SWB00658</t>
+  </si>
+  <si>
+    <t>SWB00659</t>
+  </si>
+  <si>
+    <t>SWB01679</t>
+  </si>
+  <si>
+    <t>SWB01360</t>
+  </si>
+  <si>
+    <t>SWB01801</t>
+  </si>
+  <si>
+    <t>SWB01802</t>
+  </si>
+  <si>
+    <t>SWB00804</t>
+  </si>
+  <si>
+    <t>SWB02088</t>
+  </si>
+  <si>
+    <t>SWB01410</t>
+  </si>
+  <si>
+    <t>SWB01413</t>
+  </si>
+  <si>
+    <t>SWB01414</t>
+  </si>
+  <si>
+    <t>SWB01405</t>
   </si>
   <si>
     <t>SWB01406</t>
   </si>
   <si>
-    <t>CLI-12-C-6210-03</t>
-  </si>
-  <si>
-    <t>CLI-12-C-6211-07</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6080-07</t>
-  </si>
-  <si>
-    <t>CLI-P14345-22</t>
-  </si>
-  <si>
-    <t>CLI-P19657-01</t>
-  </si>
-  <si>
-    <t>CLI-P19657-24</t>
-  </si>
-  <si>
-    <t>CLI-P19657-25</t>
-  </si>
-  <si>
-    <t>CLI-P19657-26</t>
-  </si>
-  <si>
-    <t>CLI-P19671-05</t>
-  </si>
-  <si>
-    <t>CLI-P20321S-08-01</t>
-  </si>
-  <si>
-    <t>CLI-P20325-23</t>
-  </si>
-  <si>
-    <t>CLI-P20336-01</t>
-  </si>
-  <si>
-    <t>CLI-PP10315-01</t>
-  </si>
-  <si>
-    <t>CLI-PP13629-12</t>
-  </si>
-  <si>
-    <t>CLI-PP17250-05</t>
-  </si>
-  <si>
-    <t>CLI-PP19380-03</t>
-  </si>
-  <si>
-    <t>CLI-PP22114-06</t>
-  </si>
-  <si>
-    <t>CLI-P19660-14</t>
-  </si>
-  <si>
-    <t>CLI-PP19568-02</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6101-01</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6101-02</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6101-05</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6101-06</t>
-  </si>
-  <si>
-    <t>CLI-12-D-7930-01</t>
-  </si>
-  <si>
-    <t>CLI-12-D-7930-02</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6085-07</t>
-  </si>
-  <si>
-    <t>CLI-P20330-02</t>
-  </si>
-  <si>
-    <t>CLI-PP8655</t>
-  </si>
-  <si>
-    <t>CLI-P20321-12</t>
+    <t>SWB01409</t>
+  </si>
+  <si>
+    <t>SWB00049</t>
+  </si>
+  <si>
+    <t>SWB01411</t>
+  </si>
+  <si>
+    <t>SWB01417</t>
+  </si>
+  <si>
+    <t>SWB01418</t>
+  </si>
+  <si>
+    <t>SWB01419</t>
+  </si>
+  <si>
+    <t>SWB01420</t>
+  </si>
+  <si>
+    <t>SWB01421</t>
+  </si>
+  <si>
+    <t>SWB01423</t>
+  </si>
+  <si>
+    <t>SWB01424</t>
+  </si>
+  <si>
+    <t>SWB01425</t>
+  </si>
+  <si>
+    <t>SWB01427</t>
+  </si>
+  <si>
+    <t>SWB01428</t>
+  </si>
+  <si>
+    <t>SWB01430</t>
+  </si>
+  <si>
+    <t>SWB01431</t>
+  </si>
+  <si>
+    <t>SWB01964</t>
+  </si>
+  <si>
+    <t>SWB01422</t>
+  </si>
+  <si>
+    <t>SWB01432</t>
+  </si>
+  <si>
+    <t>SWB01412</t>
+  </si>
+  <si>
+    <t>SWB01426</t>
+  </si>
+  <si>
+    <t>ISSIV00672</t>
+  </si>
+  <si>
+    <t>SWB02037</t>
+  </si>
+  <si>
+    <t>SWB02045</t>
+  </si>
+  <si>
+    <t>SWB02052</t>
+  </si>
+  <si>
+    <t>SWB02038</t>
+  </si>
+  <si>
+    <t>SWB02030</t>
+  </si>
+  <si>
+    <t>SWB02031</t>
+  </si>
+  <si>
+    <t>SWB02039</t>
+  </si>
+  <si>
+    <t>SWB02040</t>
+  </si>
+  <si>
+    <t>SWB02048</t>
+  </si>
+  <si>
+    <t>SWB02049</t>
   </si>
   <si>
     <t>SWB02034</t>
   </si>
   <si>
-    <t>CLI-PP14112-19</t>
-  </si>
-  <si>
-    <t>CLI-P20321-13</t>
-  </si>
-  <si>
-    <t>CLI-11-A-6037-01</t>
-  </si>
-  <si>
-    <t>CLI-11-D-6165-01</t>
-  </si>
-  <si>
-    <t>CLI-P20321-15-11</t>
-  </si>
-  <si>
-    <t>CLI-P20321-15-12</t>
-  </si>
-  <si>
-    <t>CLI-P20512-08</t>
-  </si>
-  <si>
-    <t>CLI-P20512-09</t>
-  </si>
-  <si>
-    <t>CLI-13-D-6196-01</t>
-  </si>
-  <si>
-    <t>CLI-P20512-18</t>
-  </si>
-  <si>
-    <t>CLI-13-D-6195-01</t>
-  </si>
-  <si>
-    <t>CLI-P20512-06</t>
-  </si>
-  <si>
-    <t>CLI-P20512-07</t>
-  </si>
-  <si>
-    <t>CLI-P17311-17</t>
-  </si>
-  <si>
-    <t>CLI-P20321-21</t>
-  </si>
-  <si>
-    <t>CLI-PP20205-121</t>
-  </si>
-  <si>
-    <t>CLI-11-A-6030-01</t>
-  </si>
-  <si>
-    <t>CLI-PP20204-06</t>
-  </si>
-  <si>
-    <t>CLI-PP20203-06</t>
-  </si>
-  <si>
-    <t>CLI-PP20205-061</t>
-  </si>
-  <si>
-    <t>SWB02015</t>
-  </si>
-  <si>
-    <t>SWB02032</t>
-  </si>
-  <si>
-    <t>CLI-P20321S-06</t>
-  </si>
-  <si>
-    <t>CLI-12-6383-01</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6015-05</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6017-02</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6234-08</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6234-06</t>
-  </si>
-  <si>
-    <t>CLI-PP20204-12</t>
-  </si>
-  <si>
-    <t>CLI-PP20204-13</t>
-  </si>
-  <si>
-    <t>CLI-PP20203-12</t>
-  </si>
-  <si>
-    <t>CLI-PP20203-13</t>
-  </si>
-  <si>
-    <t>CLI-PP13949-04</t>
-  </si>
-  <si>
-    <t>CLI-PP13949-09</t>
-  </si>
-  <si>
-    <t>CLI-PP20205-131</t>
-  </si>
-  <si>
-    <t>CLI-PP20205-132</t>
-  </si>
-  <si>
-    <t>CLI-12-6267-01</t>
-  </si>
-  <si>
-    <t>CLI-PP13949-10</t>
-  </si>
-  <si>
-    <t>CLI-PP13949-08</t>
-  </si>
-  <si>
-    <t>CLI-96-6183-01</t>
-  </si>
-  <si>
-    <t>CLI-96-6183-02</t>
-  </si>
-  <si>
-    <t>CLI-P19663-24</t>
-  </si>
-  <si>
-    <t>CLI-12-6265-01</t>
-  </si>
-  <si>
-    <t>CLI-12-D-6234-10</t>
-  </si>
-  <si>
-    <t>CLI-PP22114-05</t>
-  </si>
-  <si>
-    <t>CLI-PP7517-01</t>
-  </si>
-  <si>
-    <t>CLI-P20325-25</t>
-  </si>
-  <si>
-    <t>CLI-P20325-24</t>
-  </si>
-  <si>
-    <t>CLI-P14734-10</t>
+    <t>SWB02050</t>
+  </si>
+  <si>
+    <t>SWB02033</t>
+  </si>
+  <si>
+    <t>SWB02046</t>
+  </si>
+  <si>
+    <t>SWB02047</t>
+  </si>
+  <si>
+    <t>SWB02035</t>
+  </si>
+  <si>
+    <t>SWB02041</t>
+  </si>
+  <si>
+    <t>SWB01526</t>
+  </si>
+  <si>
+    <t>SWB02029</t>
+  </si>
+  <si>
+    <t>SWB02054</t>
+  </si>
+  <si>
+    <t>SWB02053</t>
+  </si>
+  <si>
+    <t>SWB02055</t>
+  </si>
+  <si>
+    <t>SWB02036</t>
+  </si>
+  <si>
+    <t>SWB02042</t>
+  </si>
+  <si>
+    <t>SWB02043</t>
+  </si>
+  <si>
+    <t>SWB01944</t>
+  </si>
+  <si>
+    <t>SWB00456</t>
+  </si>
+  <si>
+    <t>SWB01167</t>
+  </si>
+  <si>
+    <t>SWB01169</t>
+  </si>
+  <si>
+    <t>SWB00488</t>
+  </si>
+  <si>
+    <t>SWB01524</t>
+  </si>
+  <si>
+    <t>SWB01525</t>
+  </si>
+  <si>
+    <t>SWB01522</t>
+  </si>
+  <si>
+    <t>SWB01523</t>
+  </si>
+  <si>
+    <t>SWB01515</t>
+  </si>
+  <si>
+    <t>SWB01517</t>
+  </si>
+  <si>
+    <t>SWB01528</t>
+  </si>
+  <si>
+    <t>SWB01529</t>
+  </si>
+  <si>
+    <t>SWB01162</t>
+  </si>
+  <si>
+    <t>SWB01518</t>
+  </si>
+  <si>
+    <t>SWB02051</t>
+  </si>
+  <si>
+    <t>SWB01469</t>
+  </si>
+  <si>
+    <t>SWB01311</t>
+  </si>
+  <si>
+    <t>SWB01487</t>
+  </si>
+  <si>
+    <t>SWB01161</t>
+  </si>
+  <si>
+    <t>SWB01433</t>
+  </si>
+  <si>
+    <t>SWB01378</t>
+  </si>
+  <si>
+    <t>SWB02437</t>
+  </si>
+  <si>
+    <t>SWB02436</t>
+  </si>
+  <si>
+    <t>SWB00589</t>
   </si>
 </sst>
 </file>
@@ -2484,7 +2328,7 @@
         <v>507</v>
       </c>
       <c r="F3" t="s">
-        <v>510</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2504,7 +2348,7 @@
         <v>507</v>
       </c>
       <c r="F4" t="s">
-        <v>511</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2524,7 +2368,7 @@
         <v>507</v>
       </c>
       <c r="F5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2544,7 +2388,7 @@
         <v>507</v>
       </c>
       <c r="F6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2564,7 +2408,7 @@
         <v>507</v>
       </c>
       <c r="F7" t="s">
-        <v>514</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2584,7 +2428,7 @@
         <v>507</v>
       </c>
       <c r="F8" t="s">
-        <v>515</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2604,7 +2448,7 @@
         <v>507</v>
       </c>
       <c r="F9" t="s">
-        <v>516</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2624,7 +2468,7 @@
         <v>507</v>
       </c>
       <c r="F10" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2644,7 +2488,7 @@
         <v>507</v>
       </c>
       <c r="F11" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2664,7 +2508,7 @@
         <v>507</v>
       </c>
       <c r="F12" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2684,7 +2528,7 @@
         <v>507</v>
       </c>
       <c r="F13" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2704,7 +2548,7 @@
         <v>507</v>
       </c>
       <c r="F14" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2724,7 +2568,7 @@
         <v>507</v>
       </c>
       <c r="F15" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2744,7 +2588,7 @@
         <v>507</v>
       </c>
       <c r="F16" t="s">
-        <v>523</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2764,7 +2608,7 @@
         <v>507</v>
       </c>
       <c r="F17" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2784,7 +2628,7 @@
         <v>507</v>
       </c>
       <c r="F18" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2804,7 +2648,7 @@
         <v>507</v>
       </c>
       <c r="F19" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2824,7 +2668,7 @@
         <v>507</v>
       </c>
       <c r="F20" t="s">
-        <v>527</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2844,7 +2688,7 @@
         <v>507</v>
       </c>
       <c r="F21" t="s">
-        <v>528</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2864,7 +2708,7 @@
         <v>507</v>
       </c>
       <c r="F22" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2884,7 +2728,7 @@
         <v>507</v>
       </c>
       <c r="F23" t="s">
-        <v>530</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2904,7 +2748,7 @@
         <v>507</v>
       </c>
       <c r="F24" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2924,7 +2768,7 @@
         <v>507</v>
       </c>
       <c r="F25" t="s">
-        <v>532</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2944,7 +2788,7 @@
         <v>507</v>
       </c>
       <c r="F26" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2964,7 +2808,7 @@
         <v>507</v>
       </c>
       <c r="F27" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2984,7 +2828,7 @@
         <v>507</v>
       </c>
       <c r="F28" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -3004,7 +2848,7 @@
         <v>507</v>
       </c>
       <c r="F29" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -3024,7 +2868,7 @@
         <v>507</v>
       </c>
       <c r="F30" t="s">
-        <v>537</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -3044,7 +2888,7 @@
         <v>507</v>
       </c>
       <c r="F31" t="s">
-        <v>538</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -3064,7 +2908,7 @@
         <v>507</v>
       </c>
       <c r="F32" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -3084,7 +2928,7 @@
         <v>507</v>
       </c>
       <c r="F33" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -3104,7 +2948,7 @@
         <v>507</v>
       </c>
       <c r="F34" t="s">
-        <v>541</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -3124,7 +2968,7 @@
         <v>507</v>
       </c>
       <c r="F35" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -3144,7 +2988,7 @@
         <v>507</v>
       </c>
       <c r="F36" t="s">
-        <v>543</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -3164,7 +3008,7 @@
         <v>507</v>
       </c>
       <c r="F37" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -3184,7 +3028,7 @@
         <v>507</v>
       </c>
       <c r="F38" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -3204,7 +3048,7 @@
         <v>507</v>
       </c>
       <c r="F39" t="s">
-        <v>546</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -3224,7 +3068,7 @@
         <v>507</v>
       </c>
       <c r="F40" t="s">
-        <v>547</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -3244,7 +3088,7 @@
         <v>507</v>
       </c>
       <c r="F41" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -3264,7 +3108,7 @@
         <v>507</v>
       </c>
       <c r="F42" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -3284,7 +3128,7 @@
         <v>507</v>
       </c>
       <c r="F43" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -3304,7 +3148,7 @@
         <v>507</v>
       </c>
       <c r="F44" t="s">
-        <v>551</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -3324,7 +3168,7 @@
         <v>507</v>
       </c>
       <c r="F45" t="s">
-        <v>552</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -3344,7 +3188,7 @@
         <v>507</v>
       </c>
       <c r="F46" t="s">
-        <v>553</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -3364,7 +3208,7 @@
         <v>507</v>
       </c>
       <c r="F47" t="s">
-        <v>554</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -3384,7 +3228,7 @@
         <v>507</v>
       </c>
       <c r="F48" t="s">
-        <v>555</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -3404,7 +3248,7 @@
         <v>507</v>
       </c>
       <c r="F49" t="s">
-        <v>556</v>
+        <v>534</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -3424,7 +3268,7 @@
         <v>507</v>
       </c>
       <c r="F50" t="s">
-        <v>557</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -3444,7 +3288,7 @@
         <v>507</v>
       </c>
       <c r="F51" t="s">
-        <v>558</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -3464,7 +3308,7 @@
         <v>507</v>
       </c>
       <c r="F52" t="s">
-        <v>559</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -3484,7 +3328,7 @@
         <v>507</v>
       </c>
       <c r="F53" t="s">
-        <v>560</v>
+        <v>535</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -3504,7 +3348,7 @@
         <v>507</v>
       </c>
       <c r="F54" t="s">
-        <v>561</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -3524,7 +3368,7 @@
         <v>507</v>
       </c>
       <c r="F55" t="s">
-        <v>562</v>
+        <v>536</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -3544,7 +3388,7 @@
         <v>507</v>
       </c>
       <c r="F56" t="s">
-        <v>563</v>
+        <v>537</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -3564,7 +3408,7 @@
         <v>507</v>
       </c>
       <c r="F57" t="s">
-        <v>564</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -3584,7 +3428,7 @@
         <v>507</v>
       </c>
       <c r="F58" t="s">
-        <v>565</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -3604,7 +3448,7 @@
         <v>507</v>
       </c>
       <c r="F59" t="s">
-        <v>566</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -3624,7 +3468,7 @@
         <v>507</v>
       </c>
       <c r="F60" t="s">
-        <v>567</v>
+        <v>538</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -3644,7 +3488,7 @@
         <v>507</v>
       </c>
       <c r="F61" t="s">
-        <v>568</v>
+        <v>539</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -3664,7 +3508,7 @@
         <v>507</v>
       </c>
       <c r="F62" t="s">
-        <v>569</v>
+        <v>540</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -3684,7 +3528,7 @@
         <v>507</v>
       </c>
       <c r="F63" t="s">
-        <v>570</v>
+        <v>541</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -3704,7 +3548,7 @@
         <v>507</v>
       </c>
       <c r="F64" t="s">
-        <v>571</v>
+        <v>542</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3724,7 +3568,7 @@
         <v>507</v>
       </c>
       <c r="F65" t="s">
-        <v>572</v>
+        <v>543</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -3744,7 +3588,7 @@
         <v>507</v>
       </c>
       <c r="F66" t="s">
-        <v>573</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -3764,7 +3608,7 @@
         <v>507</v>
       </c>
       <c r="F67" t="s">
-        <v>574</v>
+        <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -3784,7 +3628,7 @@
         <v>507</v>
       </c>
       <c r="F68" t="s">
-        <v>575</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -3804,7 +3648,7 @@
         <v>507</v>
       </c>
       <c r="F69" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3824,7 +3668,7 @@
         <v>507</v>
       </c>
       <c r="F70" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -3844,7 +3688,7 @@
         <v>507</v>
       </c>
       <c r="F71" t="s">
-        <v>578</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3864,7 +3708,7 @@
         <v>507</v>
       </c>
       <c r="F72" t="s">
-        <v>579</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -3884,7 +3728,7 @@
         <v>507</v>
       </c>
       <c r="F73" t="s">
-        <v>580</v>
+        <v>546</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -3904,7 +3748,7 @@
         <v>507</v>
       </c>
       <c r="F74" t="s">
-        <v>581</v>
+        <v>547</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -3924,7 +3768,7 @@
         <v>507</v>
       </c>
       <c r="F75" t="s">
-        <v>582</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -3944,7 +3788,7 @@
         <v>507</v>
       </c>
       <c r="F76" t="s">
-        <v>583</v>
+        <v>548</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3964,7 +3808,7 @@
         <v>507</v>
       </c>
       <c r="F77" t="s">
-        <v>584</v>
+        <v>549</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3984,7 +3828,7 @@
         <v>507</v>
       </c>
       <c r="F78" t="s">
-        <v>585</v>
+        <v>550</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -4004,7 +3848,7 @@
         <v>507</v>
       </c>
       <c r="F79" t="s">
-        <v>586</v>
+        <v>551</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -4024,7 +3868,7 @@
         <v>507</v>
       </c>
       <c r="F80" t="s">
-        <v>587</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -4044,7 +3888,7 @@
         <v>507</v>
       </c>
       <c r="F81" t="s">
-        <v>588</v>
+        <v>552</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -4064,7 +3908,7 @@
         <v>507</v>
       </c>
       <c r="F82" t="s">
-        <v>589</v>
+        <v>553</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -4084,7 +3928,7 @@
         <v>507</v>
       </c>
       <c r="F83" t="s">
-        <v>590</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -4104,7 +3948,7 @@
         <v>507</v>
       </c>
       <c r="F84" t="s">
-        <v>591</v>
+        <v>88</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -4124,7 +3968,7 @@
         <v>507</v>
       </c>
       <c r="F85" t="s">
-        <v>592</v>
+        <v>89</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -4144,7 +3988,7 @@
         <v>507</v>
       </c>
       <c r="F86" t="s">
-        <v>593</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -4164,7 +4008,7 @@
         <v>507</v>
       </c>
       <c r="F87" t="s">
-        <v>594</v>
+        <v>91</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -4184,7 +4028,7 @@
         <v>507</v>
       </c>
       <c r="F88" t="s">
-        <v>595</v>
+        <v>554</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -4204,7 +4048,7 @@
         <v>507</v>
       </c>
       <c r="F89" t="s">
-        <v>596</v>
+        <v>93</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -4224,7 +4068,7 @@
         <v>507</v>
       </c>
       <c r="F90" t="s">
-        <v>597</v>
+        <v>555</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -4244,7 +4088,7 @@
         <v>507</v>
       </c>
       <c r="F91" t="s">
-        <v>598</v>
+        <v>556</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -4264,7 +4108,7 @@
         <v>507</v>
       </c>
       <c r="F92" t="s">
-        <v>599</v>
+        <v>557</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -4284,7 +4128,7 @@
         <v>507</v>
       </c>
       <c r="F93" t="s">
-        <v>600</v>
+        <v>558</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -4304,7 +4148,7 @@
         <v>507</v>
       </c>
       <c r="F94" t="s">
-        <v>601</v>
+        <v>559</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -4324,7 +4168,7 @@
         <v>507</v>
       </c>
       <c r="F95" t="s">
-        <v>602</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -4344,7 +4188,7 @@
         <v>507</v>
       </c>
       <c r="F96" t="s">
-        <v>603</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -4364,7 +4208,7 @@
         <v>507</v>
       </c>
       <c r="F97" t="s">
-        <v>604</v>
+        <v>560</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -4384,7 +4228,7 @@
         <v>507</v>
       </c>
       <c r="F98" t="s">
-        <v>605</v>
+        <v>561</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -4404,7 +4248,7 @@
         <v>507</v>
       </c>
       <c r="F99" t="s">
-        <v>606</v>
+        <v>562</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -4424,7 +4268,7 @@
         <v>507</v>
       </c>
       <c r="F100" t="s">
-        <v>607</v>
+        <v>563</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -4444,7 +4288,7 @@
         <v>507</v>
       </c>
       <c r="F101" t="s">
-        <v>608</v>
+        <v>564</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -4464,7 +4308,7 @@
         <v>507</v>
       </c>
       <c r="F102" t="s">
-        <v>609</v>
+        <v>565</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -4484,7 +4328,7 @@
         <v>507</v>
       </c>
       <c r="F103" t="s">
-        <v>610</v>
+        <v>566</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -4504,7 +4348,7 @@
         <v>507</v>
       </c>
       <c r="F104" t="s">
-        <v>611</v>
+        <v>567</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -4524,7 +4368,7 @@
         <v>507</v>
       </c>
       <c r="F105" t="s">
-        <v>612</v>
+        <v>568</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -4544,7 +4388,7 @@
         <v>507</v>
       </c>
       <c r="F106" t="s">
-        <v>613</v>
+        <v>569</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -4564,7 +4408,7 @@
         <v>507</v>
       </c>
       <c r="F107" t="s">
-        <v>614</v>
+        <v>570</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -4584,7 +4428,7 @@
         <v>507</v>
       </c>
       <c r="F108" t="s">
-        <v>615</v>
+        <v>571</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -4604,7 +4448,7 @@
         <v>507</v>
       </c>
       <c r="F109" t="s">
-        <v>616</v>
+        <v>572</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -4624,7 +4468,7 @@
         <v>507</v>
       </c>
       <c r="F110" t="s">
-        <v>617</v>
+        <v>573</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -4644,7 +4488,7 @@
         <v>507</v>
       </c>
       <c r="F111" t="s">
-        <v>618</v>
+        <v>574</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -4664,7 +4508,7 @@
         <v>507</v>
       </c>
       <c r="F112" t="s">
-        <v>619</v>
+        <v>575</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -4684,7 +4528,7 @@
         <v>507</v>
       </c>
       <c r="F113" t="s">
-        <v>620</v>
+        <v>576</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4704,7 +4548,7 @@
         <v>507</v>
       </c>
       <c r="F114" t="s">
-        <v>621</v>
+        <v>577</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -4724,7 +4568,7 @@
         <v>507</v>
       </c>
       <c r="F115" t="s">
-        <v>622</v>
+        <v>578</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4744,7 +4588,7 @@
         <v>507</v>
       </c>
       <c r="F116" t="s">
-        <v>623</v>
+        <v>579</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -4764,7 +4608,7 @@
         <v>507</v>
       </c>
       <c r="F117" t="s">
-        <v>624</v>
+        <v>580</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4784,7 +4628,7 @@
         <v>507</v>
       </c>
       <c r="F118" t="s">
-        <v>625</v>
+        <v>581</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -4804,7 +4648,7 @@
         <v>507</v>
       </c>
       <c r="F119" t="s">
-        <v>626</v>
+        <v>582</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4824,7 +4668,7 @@
         <v>507</v>
       </c>
       <c r="F120" t="s">
-        <v>627</v>
+        <v>583</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -4844,7 +4688,7 @@
         <v>507</v>
       </c>
       <c r="F121" t="s">
-        <v>628</v>
+        <v>125</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4864,7 +4708,7 @@
         <v>507</v>
       </c>
       <c r="F122" t="s">
-        <v>629</v>
+        <v>584</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -4884,7 +4728,7 @@
         <v>507</v>
       </c>
       <c r="F123" t="s">
-        <v>630</v>
+        <v>585</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -4904,7 +4748,7 @@
         <v>507</v>
       </c>
       <c r="F124" t="s">
-        <v>631</v>
+        <v>586</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -4924,7 +4768,7 @@
         <v>507</v>
       </c>
       <c r="F125" t="s">
-        <v>632</v>
+        <v>587</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -4944,7 +4788,7 @@
         <v>507</v>
       </c>
       <c r="F126" t="s">
-        <v>633</v>
+        <v>130</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4964,7 +4808,7 @@
         <v>507</v>
       </c>
       <c r="F127" t="s">
-        <v>634</v>
+        <v>131</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4984,7 +4828,7 @@
         <v>507</v>
       </c>
       <c r="F128" t="s">
-        <v>635</v>
+        <v>132</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -5004,7 +4848,7 @@
         <v>507</v>
       </c>
       <c r="F129" t="s">
-        <v>636</v>
+        <v>133</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -5024,7 +4868,7 @@
         <v>507</v>
       </c>
       <c r="F130" t="s">
-        <v>637</v>
+        <v>134</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5044,7 +4888,7 @@
         <v>507</v>
       </c>
       <c r="F131" t="s">
-        <v>638</v>
+        <v>135</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5064,7 +4908,7 @@
         <v>507</v>
       </c>
       <c r="F132" t="s">
-        <v>639</v>
+        <v>588</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5084,7 +4928,7 @@
         <v>507</v>
       </c>
       <c r="F133" t="s">
-        <v>640</v>
+        <v>589</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -5104,7 +4948,7 @@
         <v>507</v>
       </c>
       <c r="F134" t="s">
-        <v>641</v>
+        <v>590</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -5121,7 +4965,7 @@
         <v>508</v>
       </c>
       <c r="F135" t="s">
-        <v>642</v>
+        <v>591</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5138,7 +4982,7 @@
         <v>508</v>
       </c>
       <c r="F136" t="s">
-        <v>643</v>
+        <v>592</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -5155,7 +4999,7 @@
         <v>508</v>
       </c>
       <c r="F137" t="s">
-        <v>644</v>
+        <v>593</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5172,7 +5016,7 @@
         <v>508</v>
       </c>
       <c r="F138" t="s">
-        <v>645</v>
+        <v>594</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5189,7 +5033,7 @@
         <v>508</v>
       </c>
       <c r="F139" t="s">
-        <v>646</v>
+        <v>595</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -5206,7 +5050,7 @@
         <v>508</v>
       </c>
       <c r="F140" t="s">
-        <v>647</v>
+        <v>596</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -5223,7 +5067,7 @@
         <v>508</v>
       </c>
       <c r="F141" t="s">
-        <v>648</v>
+        <v>597</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5240,7 +5084,7 @@
         <v>508</v>
       </c>
       <c r="F142" t="s">
-        <v>649</v>
+        <v>598</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5257,7 +5101,7 @@
         <v>508</v>
       </c>
       <c r="F143" t="s">
-        <v>650</v>
+        <v>599</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5274,7 +5118,7 @@
         <v>508</v>
       </c>
       <c r="F144" t="s">
-        <v>651</v>
+        <v>600</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5291,7 +5135,7 @@
         <v>508</v>
       </c>
       <c r="F145" t="s">
-        <v>652</v>
+        <v>601</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5308,7 +5152,7 @@
         <v>508</v>
       </c>
       <c r="F146" t="s">
-        <v>653</v>
+        <v>602</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5325,7 +5169,7 @@
         <v>508</v>
       </c>
       <c r="F147" t="s">
-        <v>654</v>
+        <v>603</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -5342,7 +5186,7 @@
         <v>508</v>
       </c>
       <c r="F148" t="s">
-        <v>655</v>
+        <v>604</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -5359,7 +5203,7 @@
         <v>508</v>
       </c>
       <c r="F149" t="s">
-        <v>656</v>
+        <v>605</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -5376,7 +5220,7 @@
         <v>508</v>
       </c>
       <c r="F150" t="s">
-        <v>657</v>
+        <v>606</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5393,7 +5237,7 @@
         <v>508</v>
       </c>
       <c r="F151" t="s">
-        <v>658</v>
+        <v>607</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -5410,7 +5254,7 @@
         <v>508</v>
       </c>
       <c r="F152" t="s">
-        <v>659</v>
+        <v>608</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -5427,7 +5271,7 @@
         <v>508</v>
       </c>
       <c r="F153" t="s">
-        <v>660</v>
+        <v>609</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5444,7 +5288,7 @@
         <v>508</v>
       </c>
       <c r="F154" t="s">
-        <v>661</v>
+        <v>610</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5461,7 +5305,7 @@
         <v>508</v>
       </c>
       <c r="F155" t="s">
-        <v>662</v>
+        <v>611</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5478,7 +5322,7 @@
         <v>508</v>
       </c>
       <c r="F156" t="s">
-        <v>663</v>
+        <v>612</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -5495,7 +5339,7 @@
         <v>508</v>
       </c>
       <c r="F157" t="s">
-        <v>664</v>
+        <v>613</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -5512,7 +5356,7 @@
         <v>508</v>
       </c>
       <c r="F158" t="s">
-        <v>665</v>
+        <v>614</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -5529,7 +5373,7 @@
         <v>508</v>
       </c>
       <c r="F159" t="s">
-        <v>666</v>
+        <v>615</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -5546,7 +5390,7 @@
         <v>508</v>
       </c>
       <c r="F160" t="s">
-        <v>667</v>
+        <v>616</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -5563,7 +5407,7 @@
         <v>508</v>
       </c>
       <c r="F161" t="s">
-        <v>668</v>
+        <v>617</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -5580,7 +5424,7 @@
         <v>508</v>
       </c>
       <c r="F162" t="s">
-        <v>669</v>
+        <v>618</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -5597,7 +5441,7 @@
         <v>508</v>
       </c>
       <c r="F163" t="s">
-        <v>670</v>
+        <v>619</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5614,7 +5458,7 @@
         <v>508</v>
       </c>
       <c r="F164" t="s">
-        <v>671</v>
+        <v>620</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -5631,7 +5475,7 @@
         <v>508</v>
       </c>
       <c r="F165" t="s">
-        <v>672</v>
+        <v>621</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -5648,7 +5492,7 @@
         <v>508</v>
       </c>
       <c r="F166" t="s">
-        <v>673</v>
+        <v>622</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5665,7 +5509,7 @@
         <v>508</v>
       </c>
       <c r="F167" t="s">
-        <v>674</v>
+        <v>623</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5682,7 +5526,7 @@
         <v>508</v>
       </c>
       <c r="F168" t="s">
-        <v>675</v>
+        <v>624</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -5699,7 +5543,7 @@
         <v>508</v>
       </c>
       <c r="F169" t="s">
-        <v>676</v>
+        <v>625</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -5716,7 +5560,7 @@
         <v>508</v>
       </c>
       <c r="F170" t="s">
-        <v>677</v>
+        <v>626</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -5733,7 +5577,7 @@
         <v>508</v>
       </c>
       <c r="F171" t="s">
-        <v>678</v>
+        <v>627</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -5750,7 +5594,7 @@
         <v>508</v>
       </c>
       <c r="F172" t="s">
-        <v>679</v>
+        <v>628</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -5767,7 +5611,7 @@
         <v>508</v>
       </c>
       <c r="F173" t="s">
-        <v>680</v>
+        <v>629</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -5784,7 +5628,7 @@
         <v>508</v>
       </c>
       <c r="F174" t="s">
-        <v>681</v>
+        <v>630</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -5801,7 +5645,7 @@
         <v>508</v>
       </c>
       <c r="F175" t="s">
-        <v>682</v>
+        <v>631</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -5818,7 +5662,7 @@
         <v>508</v>
       </c>
       <c r="F176" t="s">
-        <v>683</v>
+        <v>632</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -5835,7 +5679,7 @@
         <v>508</v>
       </c>
       <c r="F177" t="s">
-        <v>684</v>
+        <v>633</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -5852,7 +5696,7 @@
         <v>508</v>
       </c>
       <c r="F178" t="s">
-        <v>685</v>
+        <v>634</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -5869,7 +5713,7 @@
         <v>508</v>
       </c>
       <c r="F179" t="s">
-        <v>686</v>
+        <v>635</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -5889,7 +5733,7 @@
         <v>508</v>
       </c>
       <c r="F180" t="s">
-        <v>687</v>
+        <v>184</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -5909,7 +5753,7 @@
         <v>507</v>
       </c>
       <c r="F181" t="s">
-        <v>688</v>
+        <v>636</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -5929,7 +5773,7 @@
         <v>508</v>
       </c>
       <c r="F182" t="s">
-        <v>689</v>
+        <v>637</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -5949,7 +5793,7 @@
         <v>508</v>
       </c>
       <c r="F183" t="s">
-        <v>690</v>
+        <v>638</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -5969,7 +5813,7 @@
         <v>508</v>
       </c>
       <c r="F184" t="s">
-        <v>691</v>
+        <v>639</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -5989,7 +5833,7 @@
         <v>508</v>
       </c>
       <c r="F185" t="s">
-        <v>692</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -12323,7 +12323,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
